--- a/حساب متوسط التكلفة سبتمبر ٢٠٢٦.xlsx
+++ b/حساب متوسط التكلفة سبتمبر ٢٠٢٦.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تفصيل الوصفات بأسعار سبتمبر" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سعر الكجم من الوصفات" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنتج التام آخر سبتمبر" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفراخ المفرومة (معلّق)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفراخ المفرومة (التصحيح)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المطابقة" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنهجية والاستثناءات" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
@@ -44,15 +44,15 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -153,13 +153,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,7 +174,7 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,19 +183,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,7 +219,7 @@
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,7 +227,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -872,7 +869,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>مفروم فراخ شعبي</t>
         </is>
@@ -907,8 +904,8 @@
         <f>IF(G8&gt;0,ROUND(H8/G8,4),IF(C8="","",C8))</f>
         <v/>
       </c>
-      <c r="J8" s="11" t="n">
-        <v>30</v>
+      <c r="J8" s="8" t="n">
+        <v>31.8123</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>860</v>
@@ -921,9 +918,9 @@
         <f>IF(OR(C8="",I8=""),"",I8/C8-1)</f>
         <v/>
       </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>⚠ لم يُغيَّر السعر — بيانات شراء متعارضة; فاتورة 1111115217 (09/09): «مفروم فراخ C» 1,500 كجم بسعر 57 بينما نطاق الرتبة C 30–35، وفى نفس الفاتورة «مفروم فراخ A» بسعر 30 بينما نطاق A 55–60 — السعران يبدوان معكوسين</t>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>قياسى: (أول المدة + المشتريات) بعد تصحيح سعرَى الفاتورة 1111115217</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1093,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>مفروم فراخ فاخر</t>
         </is>
@@ -1131,8 +1128,8 @@
         <f>IF(G12&gt;0,ROUND(H12/G12,4),IF(C12="","",C12))</f>
         <v/>
       </c>
-      <c r="J12" s="11" t="n">
-        <v>60</v>
+      <c r="J12" s="8" t="n">
+        <v>57.9003</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>370</v>
@@ -1145,9 +1142,9 @@
         <f>IF(OR(C12="",I12=""),"",I12/C12-1)</f>
         <v/>
       </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>⚠ لم يُغيَّر السعر — بيانات شراء متعارضة; فاتورة 1111115217 (09/09): «مفروم فراخ A» 450 كجم بسعر 30 بينما نطاق الرتبة A 55–60، وفى نفس الفاتورة «مفروم فراخ C» بسعر 57 — السعران يبدوان معكوسين</t>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>قياسى: (أول المدة + المشتريات) بعد تصحيح سعرَى الفاتورة 1111115217</t>
         </is>
       </c>
     </row>
@@ -9748,30 +9745,30 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="12" t="inlineStr">
+      <c r="A171" s="11" t="inlineStr">
         <is>
           <t>الإجمالى</t>
         </is>
       </c>
-      <c r="D171" s="13">
+      <c r="D171" s="12">
         <f>SUM(D5:D169)</f>
         <v/>
       </c>
-      <c r="F171" s="13">
+      <c r="F171" s="12">
         <f>SUM(F5:F169)</f>
         <v/>
       </c>
-      <c r="H171" s="13">
+      <c r="H171" s="12">
         <f>SUM(H5:H169)</f>
         <v/>
       </c>
-      <c r="L171" s="13">
+      <c r="L171" s="12">
         <f>SUM(L5:L169)</f>
         <v/>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="14" t="inlineStr">
+      <c r="A173" s="13" t="inlineStr">
         <is>
           <t>مجمّع اللحوم الهندى (كتف/رقبه/سن/أرباع) — متوسط واحد للبنود الأربعة</t>
         </is>
@@ -9811,7 +9808,7 @@
         <f>D174+F174</f>
         <v/>
       </c>
-      <c r="I174" s="15">
+      <c r="I174" s="14">
         <f>ROUND(H174/G174,4)</f>
         <v/>
       </c>
@@ -9831,7 +9828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9846,6 +9843,7 @@
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9855,6 +9853,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>عمودا السعر والإجمالى بعد تصحيح الفاتورة 1111115217؛ العمود الأخير = الإجمالى كما سُجّل بالتقرير.</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -9914,6 +9919,11 @@
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>رقم الفاتورة</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>الإجمالى المسجّل بالتقرير</t>
         </is>
       </c>
     </row>
@@ -9970,6 +9980,9 @@
           <t>1111115206</t>
         </is>
       </c>
+      <c r="M4" s="5" t="n">
+        <v>4640</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -10024,6 +10037,9 @@
           <t>1111115206</t>
         </is>
       </c>
+      <c r="M5" s="5" t="n">
+        <v>3280</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -10078,6 +10094,9 @@
           <t>1111115206</t>
         </is>
       </c>
+      <c r="M6" s="5" t="n">
+        <v>14750</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -10132,6 +10151,9 @@
           <t>1111115206</t>
         </is>
       </c>
+      <c r="M7" s="5" t="n">
+        <v>9500</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -10186,6 +10208,9 @@
           <t>1111115206</t>
         </is>
       </c>
+      <c r="M8" s="5" t="n">
+        <v>31000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -10240,6 +10265,9 @@
           <t>1111115206</t>
         </is>
       </c>
+      <c r="M9" s="5" t="n">
+        <v>14750</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -10294,6 +10322,9 @@
           <t>1111115212</t>
         </is>
       </c>
+      <c r="M10" s="5" t="n">
+        <v>87000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -10348,6 +10379,9 @@
           <t>1111115207</t>
         </is>
       </c>
+      <c r="M11" s="5" t="n">
+        <v>100000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -10402,6 +10436,9 @@
           <t>1111115208</t>
         </is>
       </c>
+      <c r="M12" s="5" t="n">
+        <v>7400</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -10456,6 +10493,9 @@
           <t>1111115209</t>
         </is>
       </c>
+      <c r="M13" s="5" t="n">
+        <v>15600</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -10510,6 +10550,9 @@
           <t>1111115210</t>
         </is>
       </c>
+      <c r="M14" s="5" t="n">
+        <v>11100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -10564,6 +10607,9 @@
           <t>1111115211</t>
         </is>
       </c>
+      <c r="M15" s="5" t="n">
+        <v>41600</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -10618,6 +10664,9 @@
           <t>1111115213</t>
         </is>
       </c>
+      <c r="M16" s="5" t="n">
+        <v>3200</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -10643,13 +10692,13 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="16" t="n">
         <v>262</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="15" t="n">
         <v>41920</v>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -10671,6 +10720,9 @@
         <is>
           <t>1111115214</t>
         </is>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>41920</v>
       </c>
     </row>
     <row r="18">
@@ -10726,6 +10778,9 @@
           <t>1111115214</t>
         </is>
       </c>
+      <c r="M18" s="5" t="n">
+        <v>26814.48</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -10780,6 +10835,9 @@
           <t>1111115215</t>
         </is>
       </c>
+      <c r="M19" s="5" t="n">
+        <v>28500</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -10805,13 +10863,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="16" t="n">
         <v>2.52</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="15" t="n">
         <v>3785</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -10833,6 +10891,9 @@
         <is>
           <t>1111115216</t>
         </is>
+      </c>
+      <c r="M20" s="15" t="n">
+        <v>3785</v>
       </c>
     </row>
     <row r="21">
@@ -10859,13 +10920,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="16" t="n">
         <v>1.91</v>
       </c>
-      <c r="H21" s="16" t="n">
+      <c r="H21" s="15" t="n">
         <v>1144</v>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -10887,6 +10948,9 @@
         <is>
           <t>1111115216</t>
         </is>
+      </c>
+      <c r="M21" s="15" t="n">
+        <v>1144</v>
       </c>
     </row>
     <row r="22">
@@ -10913,13 +10977,13 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G22" s="16" t="n">
         <v>262</v>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H22" s="15" t="n">
         <v>41920</v>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -10941,6 +11005,9 @@
         <is>
           <t>1111115230</t>
         </is>
+      </c>
+      <c r="M22" s="15" t="n">
+        <v>41920</v>
       </c>
     </row>
     <row r="23">
@@ -10996,6 +11063,9 @@
           <t>1111115230</t>
         </is>
       </c>
+      <c r="M23" s="5" t="n">
+        <v>42000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -11021,13 +11091,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="16" t="n">
         <v>37</v>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="15" t="n">
         <v>37000</v>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -11049,6 +11119,9 @@
         <is>
           <t>1111115231</t>
         </is>
+      </c>
+      <c r="M24" s="15" t="n">
+        <v>37000</v>
       </c>
     </row>
     <row r="25">
@@ -11075,13 +11148,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="16" t="n">
         <v>2.64</v>
       </c>
-      <c r="H25" s="16" t="n">
+      <c r="H25" s="15" t="n">
         <v>3955</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -11103,6 +11176,9 @@
         <is>
           <t>1111115239</t>
         </is>
+      </c>
+      <c r="M25" s="15" t="n">
+        <v>3955</v>
       </c>
     </row>
     <row r="26">
@@ -11158,6 +11234,9 @@
           <t>1111115239</t>
         </is>
       </c>
+      <c r="M26" s="5" t="n">
+        <v>5810</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -11183,34 +11262,37 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="G27" s="17" t="n">
-        <v>57</v>
-      </c>
-      <c r="H27" s="16" t="n">
+      <c r="G27" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>مفروم فراخ شعبي</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>نفس ربط الكود فى يوليو: الرتبة C = الدرجة الشعبية (سعر 28 مقابل 34.7 ليونيه) | ⚠ سعر مُصحّح: سُجّل بالتقرير 57 (إجمالى 85,500.00) — أكدت الإدارة أن سعرَى الرتبتين بالفاتورة معكوسان</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>1111115217</t>
+        </is>
+      </c>
+      <c r="M27" s="15" t="n">
         <v>85500</v>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>مفروم فراخ شعبي</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>نفس ربط الكود فى يوليو: الرتبة C = الدرجة الشعبية (سعر 28 مقابل 34.7 ليونيه) | ⚠ سعر يبدو معكوسًا مع السطر الآخر بنفس الفاتورة — الصنف تُرك سعره دون تغيير</t>
-        </is>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>1111115217</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -11237,34 +11319,37 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="15" t="n">
         <v>450</v>
       </c>
-      <c r="G28" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="16" t="n">
+      <c r="G28" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>25650</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>مفروم فراخ فاخر</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>نفس ربط الكود فى يوليو: الرتبة A = الدرجة الفاخرة (سعر 55–57 ≈ 58.50 ليونيه) | ⚠ سعر مُصحّح: سُجّل بالتقرير 30 (إجمالى 13,500.00) — أكدت الإدارة أن سعرَى الرتبتين بالفاتورة معكوسان</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>1111115217</t>
+        </is>
+      </c>
+      <c r="M28" s="15" t="n">
         <v>13500</v>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>مفروم فراخ فاخر</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>نفس ربط الكود فى يوليو: الرتبة A = الدرجة الفاخرة (سعر 55–57 ≈ 58.50 ليونيه) | ⚠ سعر يبدو معكوسًا مع السطر الآخر بنفس الفاتورة — الصنف تُرك سعره دون تغيير</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>1111115217</t>
-        </is>
       </c>
     </row>
     <row r="29">
@@ -11291,13 +11376,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="H29" s="16" t="n">
+      <c r="H29" s="15" t="n">
         <v>39000</v>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -11319,6 +11404,9 @@
         <is>
           <t>1111115234</t>
         </is>
+      </c>
+      <c r="M29" s="15" t="n">
+        <v>39000</v>
       </c>
     </row>
     <row r="30">
@@ -11374,6 +11462,9 @@
           <t>1111115235</t>
         </is>
       </c>
+      <c r="M30" s="5" t="n">
+        <v>28560</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -11428,6 +11519,9 @@
           <t>1111115235</t>
         </is>
       </c>
+      <c r="M31" s="5" t="n">
+        <v>31500</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -11482,6 +11576,9 @@
           <t>1111115220</t>
         </is>
       </c>
+      <c r="M32" s="5" t="n">
+        <v>37500</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -11536,6 +11633,9 @@
           <t>1111115222</t>
         </is>
       </c>
+      <c r="M33" s="5" t="n">
+        <v>5124</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -11561,13 +11661,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="15" t="n">
         <v>115</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="H34" s="16" t="n">
+      <c r="H34" s="15" t="n">
         <v>1725</v>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -11589,6 +11689,9 @@
         <is>
           <t>1111115222</t>
         </is>
+      </c>
+      <c r="M34" s="15" t="n">
+        <v>1725</v>
       </c>
     </row>
     <row r="35">
@@ -11644,6 +11747,9 @@
           <t>1111115223</t>
         </is>
       </c>
+      <c r="M35" s="5" t="n">
+        <v>45000</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -11698,6 +11804,9 @@
           <t>1111115236</t>
         </is>
       </c>
+      <c r="M36" s="5" t="n">
+        <v>42000</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -11723,13 +11832,13 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="G37" s="17" t="n">
+      <c r="G37" s="16" t="n">
         <v>262</v>
       </c>
-      <c r="H37" s="16" t="n">
+      <c r="H37" s="15" t="n">
         <v>41920</v>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -11751,6 +11860,9 @@
         <is>
           <t>1111115236</t>
         </is>
+      </c>
+      <c r="M37" s="15" t="n">
+        <v>41920</v>
       </c>
     </row>
     <row r="38">
@@ -11806,6 +11918,9 @@
           <t>1111115236</t>
         </is>
       </c>
+      <c r="M38" s="5" t="n">
+        <v>27311.76</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -11860,6 +11975,9 @@
           <t>1111115221</t>
         </is>
       </c>
+      <c r="M39" s="5" t="n">
+        <v>9800</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -11914,6 +12032,9 @@
           <t>1111115225</t>
         </is>
       </c>
+      <c r="M40" s="5" t="n">
+        <v>24375</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -11968,6 +12089,9 @@
           <t>1111115237</t>
         </is>
       </c>
+      <c r="M41" s="5" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -12022,6 +12146,9 @@
           <t>1111115238</t>
         </is>
       </c>
+      <c r="M42" s="5" t="n">
+        <v>17775</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -12076,6 +12203,9 @@
           <t>1111115227</t>
         </is>
       </c>
+      <c r="M43" s="5" t="n">
+        <v>4300</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -12130,6 +12260,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M44" s="5" t="n">
+        <v>10200</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -12184,6 +12317,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M45" s="5" t="n">
+        <v>6375</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -12238,6 +12374,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M46" s="5" t="n">
+        <v>3750</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -12292,6 +12431,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M47" s="5" t="n">
+        <v>5100</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -12346,6 +12488,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M48" s="5" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -12400,6 +12545,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M49" s="5" t="n">
+        <v>1400</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -12454,6 +12602,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M50" s="5" t="n">
+        <v>6500</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
@@ -12479,13 +12630,13 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="G51" s="17" t="n">
+      <c r="G51" s="16" t="n">
         <v>140</v>
       </c>
-      <c r="H51" s="16" t="n">
+      <c r="H51" s="15" t="n">
         <v>5600</v>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -12507,6 +12658,9 @@
         <is>
           <t>1111115226</t>
         </is>
+      </c>
+      <c r="M51" s="15" t="n">
+        <v>5600</v>
       </c>
     </row>
     <row r="52">
@@ -12562,6 +12716,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M52" s="5" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -12616,6 +12773,9 @@
           <t>1111115226</t>
         </is>
       </c>
+      <c r="M53" s="5" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -12670,6 +12830,9 @@
           <t>1111115228</t>
         </is>
       </c>
+      <c r="M54" s="5" t="n">
+        <v>9800</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -12724,6 +12887,9 @@
           <t>1111115229</t>
         </is>
       </c>
+      <c r="M55" s="5" t="n">
+        <v>24150</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -12778,6 +12944,9 @@
           <t>1111115229</t>
         </is>
       </c>
+      <c r="M56" s="5" t="n">
+        <v>27000</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
@@ -12803,13 +12972,13 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="F57" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="G57" s="17" t="n">
+      <c r="G57" s="16" t="n">
         <v>261</v>
       </c>
-      <c r="H57" s="16" t="n">
+      <c r="H57" s="15" t="n">
         <v>20880</v>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -12831,6 +13000,9 @@
         <is>
           <t>1111115243</t>
         </is>
+      </c>
+      <c r="M57" s="15" t="n">
+        <v>20880</v>
       </c>
     </row>
     <row r="58">
@@ -12886,6 +13058,9 @@
           <t>1111115263</t>
         </is>
       </c>
+      <c r="M58" s="5" t="n">
+        <v>82950</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n">
@@ -12911,13 +13086,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F59" s="16" t="n">
+      <c r="F59" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="G59" s="17" t="n">
+      <c r="G59" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="H59" s="16" t="n">
+      <c r="H59" s="15" t="n">
         <v>39000</v>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -12939,6 +13114,9 @@
         <is>
           <t>1111115244</t>
         </is>
+      </c>
+      <c r="M59" s="15" t="n">
+        <v>39000</v>
       </c>
     </row>
     <row r="60">
@@ -12994,6 +13172,9 @@
           <t>1111115245</t>
         </is>
       </c>
+      <c r="M60" s="5" t="n">
+        <v>42000</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n">
@@ -13019,13 +13200,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F61" s="16" t="n">
+      <c r="F61" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="G61" s="17" t="n">
+      <c r="G61" s="16" t="n">
         <v>132</v>
       </c>
-      <c r="H61" s="16" t="n">
+      <c r="H61" s="15" t="n">
         <v>3300</v>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -13047,6 +13228,9 @@
         <is>
           <t>1111115249</t>
         </is>
+      </c>
+      <c r="M61" s="15" t="n">
+        <v>3300</v>
       </c>
     </row>
     <row r="62">
@@ -13102,6 +13286,9 @@
           <t>1111115255</t>
         </is>
       </c>
+      <c r="M62" s="5" t="n">
+        <v>28500</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -13156,6 +13343,9 @@
           <t>1111115251</t>
         </is>
       </c>
+      <c r="M63" s="5" t="n">
+        <v>28560.51</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -13210,6 +13400,9 @@
           <t>1111115252</t>
         </is>
       </c>
+      <c r="M64" s="5" t="n">
+        <v>8600</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -13264,6 +13457,9 @@
           <t>1111115252</t>
         </is>
       </c>
+      <c r="M65" s="5" t="n">
+        <v>12400</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -13318,6 +13514,9 @@
           <t>1111115259</t>
         </is>
       </c>
+      <c r="M66" s="5" t="n">
+        <v>19800</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -13372,6 +13571,9 @@
           <t>1111115260</t>
         </is>
       </c>
+      <c r="M67" s="5" t="n">
+        <v>51000</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -13426,6 +13628,9 @@
           <t>1111115233</t>
         </is>
       </c>
+      <c r="M68" s="5" t="n">
+        <v>81250</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -13480,6 +13685,9 @@
           <t>1111115261</t>
         </is>
       </c>
+      <c r="M69" s="5" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -13534,6 +13742,9 @@
           <t>1111115261</t>
         </is>
       </c>
+      <c r="M70" s="5" t="n">
+        <v>37500</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -13588,6 +13799,9 @@
           <t>1111115261</t>
         </is>
       </c>
+      <c r="M71" s="5" t="n">
+        <v>42900</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="n">
@@ -13613,13 +13827,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F72" s="16" t="n">
+      <c r="F72" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="G72" s="17" t="n">
+      <c r="G72" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="H72" s="16" t="n">
+      <c r="H72" s="15" t="n">
         <v>39000</v>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -13641,6 +13855,9 @@
         <is>
           <t>1111115256</t>
         </is>
+      </c>
+      <c r="M72" s="15" t="n">
+        <v>39000</v>
       </c>
     </row>
     <row r="73">
@@ -13667,13 +13884,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F73" s="16" t="n">
+      <c r="F73" s="15" t="n">
         <v>725</v>
       </c>
-      <c r="G73" s="17" t="n">
+      <c r="G73" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="H73" s="16" t="n">
+      <c r="H73" s="15" t="n">
         <v>7975</v>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -13695,6 +13912,9 @@
         <is>
           <t>1111115257</t>
         </is>
+      </c>
+      <c r="M73" s="15" t="n">
+        <v>7975</v>
       </c>
     </row>
     <row r="74">
@@ -13721,13 +13941,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F74" s="16" t="n">
+      <c r="F74" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="G74" s="17" t="n">
+      <c r="G74" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="H74" s="16" t="n">
+      <c r="H74" s="15" t="n">
         <v>900</v>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -13749,6 +13969,9 @@
         <is>
           <t>1111115257</t>
         </is>
+      </c>
+      <c r="M74" s="15" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="75">
@@ -13804,6 +14027,9 @@
           <t>1111115258</t>
         </is>
       </c>
+      <c r="M75" s="5" t="n">
+        <v>42400</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="n">
@@ -13829,13 +14055,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F76" s="16" t="n">
+      <c r="F76" s="15" t="n">
         <v>1800</v>
       </c>
-      <c r="G76" s="17" t="n">
+      <c r="G76" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="H76" s="16" t="n">
+      <c r="H76" s="15" t="n">
         <v>61200</v>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -13857,6 +14083,9 @@
         <is>
           <t>1111115232</t>
         </is>
+      </c>
+      <c r="M76" s="15" t="n">
+        <v>61200</v>
       </c>
     </row>
     <row r="77">
@@ -13912,6 +14141,9 @@
           <t>1111115240</t>
         </is>
       </c>
+      <c r="M77" s="5" t="n">
+        <v>43000</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -13966,6 +14198,9 @@
           <t>1111115246</t>
         </is>
       </c>
+      <c r="M78" s="5" t="n">
+        <v>57375</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="n">
@@ -13991,13 +14226,13 @@
           <t>طبق</t>
         </is>
       </c>
-      <c r="F79" s="16" t="n">
+      <c r="F79" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="G79" s="17" t="n">
+      <c r="G79" s="16" t="n">
         <v>26.4</v>
       </c>
-      <c r="H79" s="16" t="n">
+      <c r="H79" s="15" t="n">
         <v>1320</v>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -14019,6 +14254,9 @@
         <is>
           <t>1111115247</t>
         </is>
+      </c>
+      <c r="M79" s="15" t="n">
+        <v>1320</v>
       </c>
     </row>
     <row r="80">
@@ -14074,6 +14312,9 @@
           <t>1111115264</t>
         </is>
       </c>
+      <c r="M80" s="5" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -14128,6 +14369,9 @@
           <t>1111115265</t>
         </is>
       </c>
+      <c r="M81" s="5" t="n">
+        <v>4600</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -14182,6 +14426,9 @@
           <t>1111115262</t>
         </is>
       </c>
+      <c r="M82" s="5" t="n">
+        <v>6495</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -14236,6 +14483,9 @@
           <t>1111115281</t>
         </is>
       </c>
+      <c r="M83" s="5" t="n">
+        <v>45300</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -14290,6 +14540,9 @@
           <t>1111115242</t>
         </is>
       </c>
+      <c r="M84" s="5" t="n">
+        <v>34000</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -14344,6 +14597,9 @@
           <t>1111115248</t>
         </is>
       </c>
+      <c r="M85" s="5" t="n">
+        <v>51000</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -14398,6 +14654,9 @@
           <t>1111115248</t>
         </is>
       </c>
+      <c r="M86" s="5" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -14452,6 +14711,9 @@
           <t>1111115253</t>
         </is>
       </c>
+      <c r="M87" s="5" t="n">
+        <v>29644.3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="n">
@@ -14477,13 +14739,13 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="F88" s="16" t="n">
+      <c r="F88" s="15" t="n">
         <v>113.7</v>
       </c>
-      <c r="G88" s="17" t="n">
+      <c r="G88" s="16" t="n">
         <v>124.97</v>
       </c>
-      <c r="H88" s="16" t="n">
+      <c r="H88" s="15" t="n">
         <v>14209.09</v>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -14505,6 +14767,9 @@
         <is>
           <t>1111115254</t>
         </is>
+      </c>
+      <c r="M88" s="15" t="n">
+        <v>14209.09</v>
       </c>
     </row>
     <row r="89">
@@ -14560,6 +14825,9 @@
           <t>1111115253</t>
         </is>
       </c>
+      <c r="M89" s="5" t="n">
+        <v>43000</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="n">
@@ -14585,13 +14853,13 @@
           <t>كيلو</t>
         </is>
       </c>
-      <c r="F90" s="16" t="n">
+      <c r="F90" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="G90" s="17" t="n">
+      <c r="G90" s="16" t="n">
         <v>262</v>
       </c>
-      <c r="H90" s="16" t="n">
+      <c r="H90" s="15" t="n">
         <v>20960</v>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -14613,6 +14881,9 @@
         <is>
           <t>1111115253</t>
         </is>
+      </c>
+      <c r="M90" s="15" t="n">
+        <v>20960</v>
       </c>
     </row>
     <row r="91">
@@ -14668,6 +14939,9 @@
           <t>1111115274</t>
         </is>
       </c>
+      <c r="M91" s="5" t="n">
+        <v>12750</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -14722,42 +14996,61 @@
           <t>1111115274</t>
         </is>
       </c>
+      <c r="M92" s="5" t="n">
+        <v>14000</v>
+      </c>
     </row>
     <row r="94">
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>إجمالى مشتريات سبتمبر</t>
-        </is>
-      </c>
-      <c r="H94" s="13">
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>إجمالى مشتريات سبتمبر (بعد التصحيح)</t>
+        </is>
+      </c>
+      <c r="H94" s="12">
         <f>SUM(H4:H92)</f>
         <v/>
       </c>
+      <c r="M94" s="12">
+        <f>SUM(M4:M92)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
-      <c r="D95" s="18" t="inlineStr">
+      <c r="D95" s="17" t="inlineStr">
         <is>
           <t>الإجمالى المطبوع بالتقرير</t>
         </is>
       </c>
-      <c r="H95" s="19" t="n">
+      <c r="M95" s="18" t="n">
         <v>2217803.14</v>
       </c>
     </row>
     <row r="96">
-      <c r="D96" s="18" t="inlineStr">
+      <c r="D96" s="17" t="inlineStr">
         <is>
           <t>منها: بلا مقابل بالجرد (مستبعدة)</t>
         </is>
       </c>
-      <c r="H96" s="19">
+      <c r="H96" s="18">
         <f>SUMIF(I4:I92,"— بلا مقابل —",H4:H92)</f>
         <v/>
       </c>
     </row>
+    <row r="97">
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>أثر تصحيح الفاتورة 1111115217 (بعد − كما سُجّل)</t>
+        </is>
+      </c>
+      <c r="H97" s="18">
+        <f>H94-M94</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14860,7 +15153,7 @@
         <f>IF(C5="","",B5*C5)</f>
         <v/>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="19">
         <f>IF(OR(C5="",D5=""),"",IF(ABS(C5-D5)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -14888,7 +15181,7 @@
         <f>IF(C6="","",B6*C6)</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <f>IF(OR(C6="",D6=""),"",IF(ABS(C6-D6)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -14916,7 +15209,7 @@
         <f>IF(C7="","",B7*C7)</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="19">
         <f>IF(OR(C7="",D7=""),"",IF(ABS(C7-D7)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -14944,7 +15237,7 @@
         <f>IF(C8="","",B8*C8)</f>
         <v/>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="19">
         <f>IF(OR(C8="",D8=""),"",IF(ABS(C8-D8)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -14972,7 +15265,7 @@
         <f>IF(C9="","",B9*C9)</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="19">
         <f>IF(OR(C9="",D9=""),"",IF(ABS(C9-D9)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15000,7 +15293,7 @@
         <f>IF(C10="","",B10*C10)</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="19">
         <f>IF(OR(C10="",D10=""),"",IF(ABS(C10-D10)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15028,7 +15321,7 @@
         <f>IF(C11="","",B11*C11)</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="19">
         <f>IF(OR(C11="",D11=""),"",IF(ABS(C11-D11)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15056,7 +15349,7 @@
         <f>IF(C12="","",B12*C12)</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="19">
         <f>IF(OR(C12="",D12=""),"",IF(ABS(C12-D12)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15084,7 +15377,7 @@
         <f>IF(C13="","",B13*C13)</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="19">
         <f>IF(OR(C13="",D13=""),"",IF(ABS(C13-D13)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15112,7 +15405,7 @@
         <f>IF(C14="","",B14*C14)</f>
         <v/>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="19">
         <f>IF(OR(C14="",D14=""),"",IF(ABS(C14-D14)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15140,7 +15433,7 @@
         <f>IF(C15="","",B15*C15)</f>
         <v/>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="19">
         <f>IF(OR(C15="",D15=""),"",IF(ABS(C15-D15)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15168,7 +15461,7 @@
         <f>IF(C16="","",B16*C16)</f>
         <v/>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="19">
         <f>IF(OR(C16="",D16=""),"",IF(ABS(C16-D16)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15196,7 +15489,7 @@
         <f>IF(C17="","",B17*C17)</f>
         <v/>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="19">
         <f>IF(OR(C17="",D17=""),"",IF(ABS(C17-D17)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15220,7 +15513,7 @@
         <f>IF(C18="","",B18*C18)</f>
         <v/>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="19">
         <f>IF(OR(C18="",D18=""),"",IF(ABS(C18-D18)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15248,7 +15541,7 @@
         <f>IF(C19="","",B19*C19)</f>
         <v/>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="19">
         <f>IF(OR(C19="",D19=""),"",IF(ABS(C19-D19)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15280,7 +15573,7 @@
         <f>IF(C20="","",B20*C20)</f>
         <v/>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="19">
         <f>IF(OR(C20="",D20=""),"",IF(ABS(C20-D20)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15308,7 +15601,7 @@
         <f>IF(C21="","",B21*C21)</f>
         <v/>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="19">
         <f>IF(OR(C21="",D21=""),"",IF(ABS(C21-D21)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15336,7 +15629,7 @@
         <f>IF(C22="","",B22*C22)</f>
         <v/>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="19">
         <f>IF(OR(C22="",D22=""),"",IF(ABS(C22-D22)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15364,7 +15657,7 @@
         <f>IF(C23="","",B23*C23)</f>
         <v/>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="19">
         <f>IF(OR(C23="",D23=""),"",IF(ABS(C23-D23)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15392,7 +15685,7 @@
         <f>IF(C24="","",B24*C24)</f>
         <v/>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="19">
         <f>IF(OR(C24="",D24=""),"",IF(ABS(C24-D24)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15420,7 +15713,7 @@
         <f>IF(C25="","",B25*C25)</f>
         <v/>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="19">
         <f>IF(OR(C25="",D25=""),"",IF(ABS(C25-D25)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15448,7 +15741,7 @@
         <f>IF(C26="","",B26*C26)</f>
         <v/>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="19">
         <f>IF(OR(C26="",D26=""),"",IF(ABS(C26-D26)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15476,7 +15769,7 @@
         <f>IF(C27="","",B27*C27)</f>
         <v/>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="19">
         <f>IF(OR(C27="",D27=""),"",IF(ABS(C27-D27)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15504,7 +15797,7 @@
         <f>IF(C28="","",B28*C28)</f>
         <v/>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="19">
         <f>IF(OR(C28="",D28=""),"",IF(ABS(C28-D28)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15528,7 +15821,7 @@
         <f>IF(C29="","",B29*C29)</f>
         <v/>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="19">
         <f>IF(OR(C29="",D29=""),"",IF(ABS(C29-D29)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15552,7 +15845,7 @@
         <f>IF(C30="","",B30*C30)</f>
         <v/>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="19">
         <f>IF(OR(C30="",D30=""),"",IF(ABS(C30-D30)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15580,7 +15873,7 @@
         <f>IF(C31="","",B31*C31)</f>
         <v/>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="19">
         <f>IF(OR(C31="",D31=""),"",IF(ABS(C31-D31)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15608,7 +15901,7 @@
         <f>IF(C32="","",B32*C32)</f>
         <v/>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="19">
         <f>IF(OR(C32="",D32=""),"",IF(ABS(C32-D32)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15636,7 +15929,7 @@
         <f>IF(C33="","",B33*C33)</f>
         <v/>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="19">
         <f>IF(OR(C33="",D33=""),"",IF(ABS(C33-D33)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15660,7 +15953,7 @@
         <f>IF(C34="","",B34*C34)</f>
         <v/>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="19">
         <f>IF(OR(C34="",D34=""),"",IF(ABS(C34-D34)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15688,7 +15981,7 @@
         <f>IF(C35="","",B35*C35)</f>
         <v/>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="19">
         <f>IF(OR(C35="",D35=""),"",IF(ABS(C35-D35)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15716,7 +16009,7 @@
         <f>IF(C36="","",B36*C36)</f>
         <v/>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="19">
         <f>IF(OR(C36="",D36=""),"",IF(ABS(C36-D36)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15744,7 +16037,7 @@
         <f>IF(C37="","",B37*C37)</f>
         <v/>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="19">
         <f>IF(OR(C37="",D37=""),"",IF(ABS(C37-D37)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15772,7 +16065,7 @@
         <f>IF(C38="","",B38*C38)</f>
         <v/>
       </c>
-      <c r="G38" s="20">
+      <c r="G38" s="19">
         <f>IF(OR(C38="",D38=""),"",IF(ABS(C38-D38)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15800,7 +16093,7 @@
         <f>IF(C39="","",B39*C39)</f>
         <v/>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="19">
         <f>IF(OR(C39="",D39=""),"",IF(ABS(C39-D39)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15828,7 +16121,7 @@
         <f>IF(C40="","",B40*C40)</f>
         <v/>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="19">
         <f>IF(OR(C40="",D40=""),"",IF(ABS(C40-D40)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15856,7 +16149,7 @@
         <f>IF(C41="","",B41*C41)</f>
         <v/>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="19">
         <f>IF(OR(C41="",D41=""),"",IF(ABS(C41-D41)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15884,7 +16177,7 @@
         <f>IF(C42="","",B42*C42)</f>
         <v/>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="19">
         <f>IF(OR(C42="",D42=""),"",IF(ABS(C42-D42)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15912,7 +16205,7 @@
         <f>IF(C43="","",B43*C43)</f>
         <v/>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="19">
         <f>IF(OR(C43="",D43=""),"",IF(ABS(C43-D43)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15940,7 +16233,7 @@
         <f>IF(C44="","",B44*C44)</f>
         <v/>
       </c>
-      <c r="G44" s="20">
+      <c r="G44" s="19">
         <f>IF(OR(C44="",D44=""),"",IF(ABS(C44-D44)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15968,7 +16261,7 @@
         <f>IF(C45="","",B45*C45)</f>
         <v/>
       </c>
-      <c r="G45" s="20">
+      <c r="G45" s="19">
         <f>IF(OR(C45="",D45=""),"",IF(ABS(C45-D45)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -15996,7 +16289,7 @@
         <f>IF(C46="","",B46*C46)</f>
         <v/>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="19">
         <f>IF(OR(C46="",D46=""),"",IF(ABS(C46-D46)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16024,7 +16317,7 @@
         <f>IF(C47="","",B47*C47)</f>
         <v/>
       </c>
-      <c r="G47" s="20">
+      <c r="G47" s="19">
         <f>IF(OR(C47="",D47=""),"",IF(ABS(C47-D47)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16052,7 +16345,7 @@
         <f>IF(C48="","",B48*C48)</f>
         <v/>
       </c>
-      <c r="G48" s="20">
+      <c r="G48" s="19">
         <f>IF(OR(C48="",D48=""),"",IF(ABS(C48-D48)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16080,7 +16373,7 @@
         <f>IF(C49="","",B49*C49)</f>
         <v/>
       </c>
-      <c r="G49" s="20">
+      <c r="G49" s="19">
         <f>IF(OR(C49="",D49=""),"",IF(ABS(C49-D49)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16108,7 +16401,7 @@
         <f>IF(C50="","",B50*C50)</f>
         <v/>
       </c>
-      <c r="G50" s="20">
+      <c r="G50" s="19">
         <f>IF(OR(C50="",D50=""),"",IF(ABS(C50-D50)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16136,7 +16429,7 @@
         <f>IF(C51="","",B51*C51)</f>
         <v/>
       </c>
-      <c r="G51" s="20">
+      <c r="G51" s="19">
         <f>IF(OR(C51="",D51=""),"",IF(ABS(C51-D51)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16164,7 +16457,7 @@
         <f>IF(C52="","",B52*C52)</f>
         <v/>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="19">
         <f>IF(OR(C52="",D52=""),"",IF(ABS(C52-D52)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16192,7 +16485,7 @@
         <f>IF(C53="","",B53*C53)</f>
         <v/>
       </c>
-      <c r="G53" s="20">
+      <c r="G53" s="19">
         <f>IF(OR(C53="",D53=""),"",IF(ABS(C53-D53)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16220,7 +16513,7 @@
         <f>IF(C54="","",B54*C54)</f>
         <v/>
       </c>
-      <c r="G54" s="20">
+      <c r="G54" s="19">
         <f>IF(OR(C54="",D54=""),"",IF(ABS(C54-D54)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16248,7 +16541,7 @@
         <f>IF(C55="","",B55*C55)</f>
         <v/>
       </c>
-      <c r="G55" s="20">
+      <c r="G55" s="19">
         <f>IF(OR(C55="",D55=""),"",IF(ABS(C55-D55)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16276,7 +16569,7 @@
         <f>IF(C56="","",B56*C56)</f>
         <v/>
       </c>
-      <c r="G56" s="20">
+      <c r="G56" s="19">
         <f>IF(OR(C56="",D56=""),"",IF(ABS(C56-D56)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16304,7 +16597,7 @@
         <f>IF(C57="","",B57*C57)</f>
         <v/>
       </c>
-      <c r="G57" s="20">
+      <c r="G57" s="19">
         <f>IF(OR(C57="",D57=""),"",IF(ABS(C57-D57)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16332,7 +16625,7 @@
         <f>IF(C58="","",B58*C58)</f>
         <v/>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="19">
         <f>IF(OR(C58="",D58=""),"",IF(ABS(C58-D58)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16360,7 +16653,7 @@
         <f>IF(C59="","",B59*C59)</f>
         <v/>
       </c>
-      <c r="G59" s="20">
+      <c r="G59" s="19">
         <f>IF(OR(C59="",D59=""),"",IF(ABS(C59-D59)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16388,7 +16681,7 @@
         <f>IF(C60="","",B60*C60)</f>
         <v/>
       </c>
-      <c r="G60" s="20">
+      <c r="G60" s="19">
         <f>IF(OR(C60="",D60=""),"",IF(ABS(C60-D60)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16416,7 +16709,7 @@
         <f>IF(C61="","",B61*C61)</f>
         <v/>
       </c>
-      <c r="G61" s="20">
+      <c r="G61" s="19">
         <f>IF(OR(C61="",D61=""),"",IF(ABS(C61-D61)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16444,7 +16737,7 @@
         <f>IF(C62="","",B62*C62)</f>
         <v/>
       </c>
-      <c r="G62" s="20">
+      <c r="G62" s="19">
         <f>IF(OR(C62="",D62=""),"",IF(ABS(C62-D62)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16472,7 +16765,7 @@
         <f>IF(C63="","",B63*C63)</f>
         <v/>
       </c>
-      <c r="G63" s="20">
+      <c r="G63" s="19">
         <f>IF(OR(C63="",D63=""),"",IF(ABS(C63-D63)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16500,7 +16793,7 @@
         <f>IF(C64="","",B64*C64)</f>
         <v/>
       </c>
-      <c r="G64" s="20">
+      <c r="G64" s="19">
         <f>IF(OR(C64="",D64=""),"",IF(ABS(C64-D64)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16524,7 +16817,7 @@
         <f>IF(C65="","",B65*C65)</f>
         <v/>
       </c>
-      <c r="G65" s="20">
+      <c r="G65" s="19">
         <f>IF(OR(C65="",D65=""),"",IF(ABS(C65-D65)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16552,7 +16845,7 @@
         <f>IF(C66="","",B66*C66)</f>
         <v/>
       </c>
-      <c r="G66" s="20">
+      <c r="G66" s="19">
         <f>IF(OR(C66="",D66=""),"",IF(ABS(C66-D66)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16580,7 +16873,7 @@
         <f>IF(C67="","",B67*C67)</f>
         <v/>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="19">
         <f>IF(OR(C67="",D67=""),"",IF(ABS(C67-D67)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16608,7 +16901,7 @@
         <f>IF(C68="","",B68*C68)</f>
         <v/>
       </c>
-      <c r="G68" s="20">
+      <c r="G68" s="19">
         <f>IF(OR(C68="",D68=""),"",IF(ABS(C68-D68)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16636,7 +16929,7 @@
         <f>IF(C69="","",B69*C69)</f>
         <v/>
       </c>
-      <c r="G69" s="20">
+      <c r="G69" s="19">
         <f>IF(OR(C69="",D69=""),"",IF(ABS(C69-D69)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16664,7 +16957,7 @@
         <f>IF(C70="","",B70*C70)</f>
         <v/>
       </c>
-      <c r="G70" s="20">
+      <c r="G70" s="19">
         <f>IF(OR(C70="",D70=""),"",IF(ABS(C70-D70)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16688,7 +16981,7 @@
         <f>IF(C71="","",B71*C71)</f>
         <v/>
       </c>
-      <c r="G71" s="20">
+      <c r="G71" s="19">
         <f>IF(OR(C71="",D71=""),"",IF(ABS(C71-D71)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16716,7 +17009,7 @@
         <f>IF(C72="","",B72*C72)</f>
         <v/>
       </c>
-      <c r="G72" s="20">
+      <c r="G72" s="19">
         <f>IF(OR(C72="",D72=""),"",IF(ABS(C72-D72)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16744,7 +17037,7 @@
         <f>IF(C73="","",B73*C73)</f>
         <v/>
       </c>
-      <c r="G73" s="20">
+      <c r="G73" s="19">
         <f>IF(OR(C73="",D73=""),"",IF(ABS(C73-D73)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16772,7 +17065,7 @@
         <f>IF(C74="","",B74*C74)</f>
         <v/>
       </c>
-      <c r="G74" s="20">
+      <c r="G74" s="19">
         <f>IF(OR(C74="",D74=""),"",IF(ABS(C74-D74)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16800,7 +17093,7 @@
         <f>IF(C75="","",B75*C75)</f>
         <v/>
       </c>
-      <c r="G75" s="20">
+      <c r="G75" s="19">
         <f>IF(OR(C75="",D75=""),"",IF(ABS(C75-D75)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16828,7 +17121,7 @@
         <f>IF(C76="","",B76*C76)</f>
         <v/>
       </c>
-      <c r="G76" s="20">
+      <c r="G76" s="19">
         <f>IF(OR(C76="",D76=""),"",IF(ABS(C76-D76)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16856,7 +17149,7 @@
         <f>IF(C77="","",B77*C77)</f>
         <v/>
       </c>
-      <c r="G77" s="20">
+      <c r="G77" s="19">
         <f>IF(OR(C77="",D77=""),"",IF(ABS(C77-D77)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16880,7 +17173,7 @@
         <f>IF(C78="","",B78*C78)</f>
         <v/>
       </c>
-      <c r="G78" s="20">
+      <c r="G78" s="19">
         <f>IF(OR(C78="",D78=""),"",IF(ABS(C78-D78)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16912,7 +17205,7 @@
         <f>IF(C79="","",B79*C79)</f>
         <v/>
       </c>
-      <c r="G79" s="20">
+      <c r="G79" s="19">
         <f>IF(OR(C79="",D79=""),"",IF(ABS(C79-D79)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16940,7 +17233,7 @@
         <f>IF(C80="","",B80*C80)</f>
         <v/>
       </c>
-      <c r="G80" s="20">
+      <c r="G80" s="19">
         <f>IF(OR(C80="",D80=""),"",IF(ABS(C80-D80)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16968,7 +17261,7 @@
         <f>IF(C81="","",B81*C81)</f>
         <v/>
       </c>
-      <c r="G81" s="20">
+      <c r="G81" s="19">
         <f>IF(OR(C81="",D81=""),"",IF(ABS(C81-D81)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -16996,7 +17289,7 @@
         <f>IF(C82="","",B82*C82)</f>
         <v/>
       </c>
-      <c r="G82" s="20">
+      <c r="G82" s="19">
         <f>IF(OR(C82="",D82=""),"",IF(ABS(C82-D82)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17020,7 +17313,7 @@
         <f>IF(C83="","",B83*C83)</f>
         <v/>
       </c>
-      <c r="G83" s="20">
+      <c r="G83" s="19">
         <f>IF(OR(C83="",D83=""),"",IF(ABS(C83-D83)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17048,7 +17341,7 @@
         <f>IF(C84="","",B84*C84)</f>
         <v/>
       </c>
-      <c r="G84" s="20">
+      <c r="G84" s="19">
         <f>IF(OR(C84="",D84=""),"",IF(ABS(C84-D84)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17076,7 +17369,7 @@
         <f>IF(C85="","",B85*C85)</f>
         <v/>
       </c>
-      <c r="G85" s="20">
+      <c r="G85" s="19">
         <f>IF(OR(C85="",D85=""),"",IF(ABS(C85-D85)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17104,7 +17397,7 @@
         <f>IF(C86="","",B86*C86)</f>
         <v/>
       </c>
-      <c r="G86" s="20">
+      <c r="G86" s="19">
         <f>IF(OR(C86="",D86=""),"",IF(ABS(C86-D86)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17132,7 +17425,7 @@
         <f>IF(C87="","",B87*C87)</f>
         <v/>
       </c>
-      <c r="G87" s="20">
+      <c r="G87" s="19">
         <f>IF(OR(C87="",D87=""),"",IF(ABS(C87-D87)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17160,7 +17453,7 @@
         <f>IF(C88="","",B88*C88)</f>
         <v/>
       </c>
-      <c r="G88" s="20">
+      <c r="G88" s="19">
         <f>IF(OR(C88="",D88=""),"",IF(ABS(C88-D88)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17188,7 +17481,7 @@
         <f>IF(C89="","",B89*C89)</f>
         <v/>
       </c>
-      <c r="G89" s="20">
+      <c r="G89" s="19">
         <f>IF(OR(C89="",D89=""),"",IF(ABS(C89-D89)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17216,7 +17509,7 @@
         <f>IF(C90="","",B90*C90)</f>
         <v/>
       </c>
-      <c r="G90" s="20">
+      <c r="G90" s="19">
         <f>IF(OR(C90="",D90=""),"",IF(ABS(C90-D90)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17244,7 +17537,7 @@
         <f>IF(C91="","",B91*C91)</f>
         <v/>
       </c>
-      <c r="G91" s="20">
+      <c r="G91" s="19">
         <f>IF(OR(C91="",D91=""),"",IF(ABS(C91-D91)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17272,7 +17565,7 @@
         <f>IF(C92="","",B92*C92)</f>
         <v/>
       </c>
-      <c r="G92" s="20">
+      <c r="G92" s="19">
         <f>IF(OR(C92="",D92=""),"",IF(ABS(C92-D92)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17300,7 +17593,7 @@
         <f>IF(C93="","",B93*C93)</f>
         <v/>
       </c>
-      <c r="G93" s="20">
+      <c r="G93" s="19">
         <f>IF(OR(C93="",D93=""),"",IF(ABS(C93-D93)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17328,7 +17621,7 @@
         <f>IF(C94="","",B94*C94)</f>
         <v/>
       </c>
-      <c r="G94" s="20">
+      <c r="G94" s="19">
         <f>IF(OR(C94="",D94=""),"",IF(ABS(C94-D94)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17356,7 +17649,7 @@
         <f>IF(C95="","",B95*C95)</f>
         <v/>
       </c>
-      <c r="G95" s="20">
+      <c r="G95" s="19">
         <f>IF(OR(C95="",D95=""),"",IF(ABS(C95-D95)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17380,7 +17673,7 @@
         <f>IF(C96="","",B96*C96)</f>
         <v/>
       </c>
-      <c r="G96" s="20">
+      <c r="G96" s="19">
         <f>IF(OR(C96="",D96=""),"",IF(ABS(C96-D96)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17408,7 +17701,7 @@
         <f>IF(C97="","",B97*C97)</f>
         <v/>
       </c>
-      <c r="G97" s="20">
+      <c r="G97" s="19">
         <f>IF(OR(C97="",D97=""),"",IF(ABS(C97-D97)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17436,7 +17729,7 @@
         <f>IF(C98="","",B98*C98)</f>
         <v/>
       </c>
-      <c r="G98" s="20">
+      <c r="G98" s="19">
         <f>IF(OR(C98="",D98=""),"",IF(ABS(C98-D98)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17464,7 +17757,7 @@
         <f>IF(C99="","",B99*C99)</f>
         <v/>
       </c>
-      <c r="G99" s="20">
+      <c r="G99" s="19">
         <f>IF(OR(C99="",D99=""),"",IF(ABS(C99-D99)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17492,7 +17785,7 @@
         <f>IF(C100="","",B100*C100)</f>
         <v/>
       </c>
-      <c r="G100" s="20">
+      <c r="G100" s="19">
         <f>IF(OR(C100="",D100=""),"",IF(ABS(C100-D100)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17520,7 +17813,7 @@
         <f>IF(C101="","",B101*C101)</f>
         <v/>
       </c>
-      <c r="G101" s="20">
+      <c r="G101" s="19">
         <f>IF(OR(C101="",D101=""),"",IF(ABS(C101-D101)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17548,7 +17841,7 @@
         <f>IF(C102="","",B102*C102)</f>
         <v/>
       </c>
-      <c r="G102" s="20">
+      <c r="G102" s="19">
         <f>IF(OR(C102="",D102=""),"",IF(ABS(C102-D102)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17576,7 +17869,7 @@
         <f>IF(C103="","",B103*C103)</f>
         <v/>
       </c>
-      <c r="G103" s="20">
+      <c r="G103" s="19">
         <f>IF(OR(C103="",D103=""),"",IF(ABS(C103-D103)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17604,7 +17897,7 @@
         <f>IF(C104="","",B104*C104)</f>
         <v/>
       </c>
-      <c r="G104" s="20">
+      <c r="G104" s="19">
         <f>IF(OR(C104="",D104=""),"",IF(ABS(C104-D104)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17632,7 +17925,7 @@
         <f>IF(C105="","",B105*C105)</f>
         <v/>
       </c>
-      <c r="G105" s="20">
+      <c r="G105" s="19">
         <f>IF(OR(C105="",D105=""),"",IF(ABS(C105-D105)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17660,7 +17953,7 @@
         <f>IF(C106="","",B106*C106)</f>
         <v/>
       </c>
-      <c r="G106" s="20">
+      <c r="G106" s="19">
         <f>IF(OR(C106="",D106=""),"",IF(ABS(C106-D106)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17688,7 +17981,7 @@
         <f>IF(C107="","",B107*C107)</f>
         <v/>
       </c>
-      <c r="G107" s="20">
+      <c r="G107" s="19">
         <f>IF(OR(C107="",D107=""),"",IF(ABS(C107-D107)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17712,7 +18005,7 @@
         <f>IF(C108="","",B108*C108)</f>
         <v/>
       </c>
-      <c r="G108" s="20">
+      <c r="G108" s="19">
         <f>IF(OR(C108="",D108=""),"",IF(ABS(C108-D108)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17736,7 +18029,7 @@
         <f>IF(C109="","",B109*C109)</f>
         <v/>
       </c>
-      <c r="G109" s="20">
+      <c r="G109" s="19">
         <f>IF(OR(C109="",D109=""),"",IF(ABS(C109-D109)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17760,7 +18053,7 @@
         <f>IF(C110="","",B110*C110)</f>
         <v/>
       </c>
-      <c r="G110" s="20">
+      <c r="G110" s="19">
         <f>IF(OR(C110="",D110=""),"",IF(ABS(C110-D110)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17788,7 +18081,7 @@
         <f>IF(C111="","",B111*C111)</f>
         <v/>
       </c>
-      <c r="G111" s="20">
+      <c r="G111" s="19">
         <f>IF(OR(C111="",D111=""),"",IF(ABS(C111-D111)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17816,7 +18109,7 @@
         <f>IF(C112="","",B112*C112)</f>
         <v/>
       </c>
-      <c r="G112" s="20">
+      <c r="G112" s="19">
         <f>IF(OR(C112="",D112=""),"",IF(ABS(C112-D112)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17840,7 +18133,7 @@
         <f>IF(C113="","",B113*C113)</f>
         <v/>
       </c>
-      <c r="G113" s="20">
+      <c r="G113" s="19">
         <f>IF(OR(C113="",D113=""),"",IF(ABS(C113-D113)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17868,7 +18161,7 @@
         <f>IF(C114="","",B114*C114)</f>
         <v/>
       </c>
-      <c r="G114" s="20">
+      <c r="G114" s="19">
         <f>IF(OR(C114="",D114=""),"",IF(ABS(C114-D114)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17896,7 +18189,7 @@
         <f>IF(C115="","",B115*C115)</f>
         <v/>
       </c>
-      <c r="G115" s="20">
+      <c r="G115" s="19">
         <f>IF(OR(C115="",D115=""),"",IF(ABS(C115-D115)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17924,7 +18217,7 @@
         <f>IF(C116="","",B116*C116)</f>
         <v/>
       </c>
-      <c r="G116" s="20">
+      <c r="G116" s="19">
         <f>IF(OR(C116="",D116=""),"",IF(ABS(C116-D116)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17952,7 +18245,7 @@
         <f>IF(C117="","",B117*C117)</f>
         <v/>
       </c>
-      <c r="G117" s="20">
+      <c r="G117" s="19">
         <f>IF(OR(C117="",D117=""),"",IF(ABS(C117-D117)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -17980,7 +18273,7 @@
         <f>IF(C118="","",B118*C118)</f>
         <v/>
       </c>
-      <c r="G118" s="20">
+      <c r="G118" s="19">
         <f>IF(OR(C118="",D118=""),"",IF(ABS(C118-D118)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18008,7 +18301,7 @@
         <f>IF(C119="","",B119*C119)</f>
         <v/>
       </c>
-      <c r="G119" s="20">
+      <c r="G119" s="19">
         <f>IF(OR(C119="",D119=""),"",IF(ABS(C119-D119)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18036,7 +18329,7 @@
         <f>IF(C120="","",B120*C120)</f>
         <v/>
       </c>
-      <c r="G120" s="20">
+      <c r="G120" s="19">
         <f>IF(OR(C120="",D120=""),"",IF(ABS(C120-D120)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18060,7 +18353,7 @@
         <f>IF(C121="","",B121*C121)</f>
         <v/>
       </c>
-      <c r="G121" s="20">
+      <c r="G121" s="19">
         <f>IF(OR(C121="",D121=""),"",IF(ABS(C121-D121)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18082,7 +18375,7 @@
         <f>IF(C122="","",B122*C122)</f>
         <v/>
       </c>
-      <c r="G122" s="20">
+      <c r="G122" s="19">
         <f>IF(OR(C122="",D122=""),"",IF(ABS(C122-D122)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18110,7 +18403,7 @@
         <f>IF(C123="","",B123*C123)</f>
         <v/>
       </c>
-      <c r="G123" s="20">
+      <c r="G123" s="19">
         <f>IF(OR(C123="",D123=""),"",IF(ABS(C123-D123)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18138,7 +18431,7 @@
         <f>IF(C124="","",B124*C124)</f>
         <v/>
       </c>
-      <c r="G124" s="20">
+      <c r="G124" s="19">
         <f>IF(OR(C124="",D124=""),"",IF(ABS(C124-D124)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18162,7 +18455,7 @@
         <f>IF(C125="","",B125*C125)</f>
         <v/>
       </c>
-      <c r="G125" s="20">
+      <c r="G125" s="19">
         <f>IF(OR(C125="",D125=""),"",IF(ABS(C125-D125)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18190,7 +18483,7 @@
         <f>IF(C126="","",B126*C126)</f>
         <v/>
       </c>
-      <c r="G126" s="20">
+      <c r="G126" s="19">
         <f>IF(OR(C126="",D126=""),"",IF(ABS(C126-D126)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18218,7 +18511,7 @@
         <f>IF(C127="","",B127*C127)</f>
         <v/>
       </c>
-      <c r="G127" s="20">
+      <c r="G127" s="19">
         <f>IF(OR(C127="",D127=""),"",IF(ABS(C127-D127)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18246,7 +18539,7 @@
         <f>IF(C128="","",B128*C128)</f>
         <v/>
       </c>
-      <c r="G128" s="20">
+      <c r="G128" s="19">
         <f>IF(OR(C128="",D128=""),"",IF(ABS(C128-D128)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18270,7 +18563,7 @@
         <f>IF(C129="","",B129*C129)</f>
         <v/>
       </c>
-      <c r="G129" s="20">
+      <c r="G129" s="19">
         <f>IF(OR(C129="",D129=""),"",IF(ABS(C129-D129)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18298,7 +18591,7 @@
         <f>IF(C130="","",B130*C130)</f>
         <v/>
       </c>
-      <c r="G130" s="20">
+      <c r="G130" s="19">
         <f>IF(OR(C130="",D130=""),"",IF(ABS(C130-D130)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18326,7 +18619,7 @@
         <f>IF(C131="","",B131*C131)</f>
         <v/>
       </c>
-      <c r="G131" s="20">
+      <c r="G131" s="19">
         <f>IF(OR(C131="",D131=""),"",IF(ABS(C131-D131)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18354,7 +18647,7 @@
         <f>IF(C132="","",B132*C132)</f>
         <v/>
       </c>
-      <c r="G132" s="20">
+      <c r="G132" s="19">
         <f>IF(OR(C132="",D132=""),"",IF(ABS(C132-D132)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18382,7 +18675,7 @@
         <f>IF(C133="","",B133*C133)</f>
         <v/>
       </c>
-      <c r="G133" s="20">
+      <c r="G133" s="19">
         <f>IF(OR(C133="",D133=""),"",IF(ABS(C133-D133)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18406,7 +18699,7 @@
         <f>IF(C134="","",B134*C134)</f>
         <v/>
       </c>
-      <c r="G134" s="20">
+      <c r="G134" s="19">
         <f>IF(OR(C134="",D134=""),"",IF(ABS(C134-D134)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18430,7 +18723,7 @@
         <f>IF(C135="","",B135*C135)</f>
         <v/>
       </c>
-      <c r="G135" s="20">
+      <c r="G135" s="19">
         <f>IF(OR(C135="",D135=""),"",IF(ABS(C135-D135)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18454,7 +18747,7 @@
         <f>IF(C136="","",B136*C136)</f>
         <v/>
       </c>
-      <c r="G136" s="20">
+      <c r="G136" s="19">
         <f>IF(OR(C136="",D136=""),"",IF(ABS(C136-D136)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18478,7 +18771,7 @@
         <f>IF(C137="","",B137*C137)</f>
         <v/>
       </c>
-      <c r="G137" s="20">
+      <c r="G137" s="19">
         <f>IF(OR(C137="",D137=""),"",IF(ABS(C137-D137)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18502,7 +18795,7 @@
         <f>IF(C138="","",B138*C138)</f>
         <v/>
       </c>
-      <c r="G138" s="20">
+      <c r="G138" s="19">
         <f>IF(OR(C138="",D138=""),"",IF(ABS(C138-D138)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18526,7 +18819,7 @@
         <f>IF(C139="","",B139*C139)</f>
         <v/>
       </c>
-      <c r="G139" s="20">
+      <c r="G139" s="19">
         <f>IF(OR(C139="",D139=""),"",IF(ABS(C139-D139)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18554,7 +18847,7 @@
         <f>IF(C140="","",B140*C140)</f>
         <v/>
       </c>
-      <c r="G140" s="20">
+      <c r="G140" s="19">
         <f>IF(OR(C140="",D140=""),"",IF(ABS(C140-D140)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18582,7 +18875,7 @@
         <f>IF(C141="","",B141*C141)</f>
         <v/>
       </c>
-      <c r="G141" s="20">
+      <c r="G141" s="19">
         <f>IF(OR(C141="",D141=""),"",IF(ABS(C141-D141)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18606,7 +18899,7 @@
         <f>IF(C142="","",B142*C142)</f>
         <v/>
       </c>
-      <c r="G142" s="20">
+      <c r="G142" s="19">
         <f>IF(OR(C142="",D142=""),"",IF(ABS(C142-D142)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18634,7 +18927,7 @@
         <f>IF(C143="","",B143*C143)</f>
         <v/>
       </c>
-      <c r="G143" s="20">
+      <c r="G143" s="19">
         <f>IF(OR(C143="",D143=""),"",IF(ABS(C143-D143)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18666,7 +18959,7 @@
         <f>IF(C144="","",B144*C144)</f>
         <v/>
       </c>
-      <c r="G144" s="20">
+      <c r="G144" s="19">
         <f>IF(OR(C144="",D144=""),"",IF(ABS(C144-D144)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18690,7 +18983,7 @@
         <f>IF(C145="","",B145*C145)</f>
         <v/>
       </c>
-      <c r="G145" s="20">
+      <c r="G145" s="19">
         <f>IF(OR(C145="",D145=""),"",IF(ABS(C145-D145)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18714,7 +19007,7 @@
         <f>IF(C146="","",B146*C146)</f>
         <v/>
       </c>
-      <c r="G146" s="20">
+      <c r="G146" s="19">
         <f>IF(OR(C146="",D146=""),"",IF(ABS(C146-D146)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18742,7 +19035,7 @@
         <f>IF(C147="","",B147*C147)</f>
         <v/>
       </c>
-      <c r="G147" s="20">
+      <c r="G147" s="19">
         <f>IF(OR(C147="",D147=""),"",IF(ABS(C147-D147)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18766,7 +19059,7 @@
         <f>IF(C148="","",B148*C148)</f>
         <v/>
       </c>
-      <c r="G148" s="20">
+      <c r="G148" s="19">
         <f>IF(OR(C148="",D148=""),"",IF(ABS(C148-D148)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18790,7 +19083,7 @@
         <f>IF(C149="","",B149*C149)</f>
         <v/>
       </c>
-      <c r="G149" s="20">
+      <c r="G149" s="19">
         <f>IF(OR(C149="",D149=""),"",IF(ABS(C149-D149)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18818,7 +19111,7 @@
         <f>IF(C150="","",B150*C150)</f>
         <v/>
       </c>
-      <c r="G150" s="20">
+      <c r="G150" s="19">
         <f>IF(OR(C150="",D150=""),"",IF(ABS(C150-D150)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18842,7 +19135,7 @@
         <f>IF(C151="","",B151*C151)</f>
         <v/>
       </c>
-      <c r="G151" s="20">
+      <c r="G151" s="19">
         <f>IF(OR(C151="",D151=""),"",IF(ABS(C151-D151)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18866,7 +19159,7 @@
         <f>IF(C152="","",B152*C152)</f>
         <v/>
       </c>
-      <c r="G152" s="20">
+      <c r="G152" s="19">
         <f>IF(OR(C152="",D152=""),"",IF(ABS(C152-D152)&lt;0.00005,"✔","✘"))</f>
         <v/>
       </c>
@@ -18877,23 +19170,23 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="12" t="inlineStr">
+      <c r="A154" s="11" t="inlineStr">
         <is>
           <t>إجمالى قيمة أول المدة (= مخزون الخامات آخر أغسطس)</t>
         </is>
       </c>
-      <c r="F154" s="13">
+      <c r="F154" s="12">
         <f>SUM(F5:F152)</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="18" t="inlineStr">
+      <c r="A155" s="17" t="inlineStr">
         <is>
           <t>إجمالى ملف «-2» (للمطابقة)</t>
         </is>
       </c>
-      <c r="F155" s="19" t="n">
+      <c r="F155" s="18" t="n">
         <v>2661861.09</v>
       </c>
     </row>
@@ -18995,7 +19288,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="F4" s="6">
@@ -19033,7 +19326,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="20" t="n">
         <v>0.32</v>
       </c>
       <c r="F5" s="6">
@@ -19071,7 +19364,7 @@
           <t>زيوت بسطرمه</t>
         </is>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="20" t="n">
         <v>0.04</v>
       </c>
       <c r="F6" s="6">
@@ -19109,7 +19402,7 @@
           <t>طعم سجق بودر</t>
         </is>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <v>0.06</v>
       </c>
       <c r="F7" s="6">
@@ -19147,7 +19440,7 @@
           <t>فلفل اسود</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <v>0.08</v>
       </c>
       <c r="F8" s="6">
@@ -19185,7 +19478,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="6">
@@ -19223,7 +19516,7 @@
           <t>بابريكا</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F10" s="6">
@@ -19261,7 +19554,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
@@ -19298,7 +19591,7 @@
           <t>قرنفل</t>
         </is>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <v>0.04</v>
       </c>
       <c r="F12" s="6">
@@ -19336,7 +19629,7 @@
           <t>قرفه</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="6">
@@ -19374,7 +19667,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="F14" s="6">
@@ -19412,7 +19705,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="20" t="n">
         <v>1.8</v>
       </c>
       <c r="F15" s="6">
@@ -19450,7 +19743,7 @@
           <t>ينسون</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="F16" s="6">
@@ -19488,7 +19781,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F17" s="6">
@@ -19526,7 +19819,7 @@
           <t>حبهان</t>
         </is>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="20" t="n">
         <v>0.03</v>
       </c>
       <c r="F18" s="6">
@@ -19544,25 +19837,25 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>سجق ابوهاشم</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>إجمالى خلطة فرعية (توابل)</t>
         </is>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="22">
         <f>SUM(E4:E18)</f>
         <v/>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="14">
         <f>G19/E19</f>
         <v/>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="23">
         <f>SUM(G4:G18)</f>
         <v/>
       </c>
@@ -19588,20 +19881,20 @@
           <t>مفروم فراخ فاخر</t>
         </is>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="F21" s="17">
-        <f>'احتساب متوسط سبتمبر'!C12</f>
+      <c r="F21" s="6">
+        <f>'احتساب متوسط سبتمبر'!I12</f>
         <v/>
       </c>
       <c r="G21" s="5">
         <f>E21*F21</f>
         <v/>
       </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19919,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="20" t="n">
         <v>10</v>
       </c>
       <c r="F22" s="6">
@@ -19664,7 +19957,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="20" t="n">
         <v>10</v>
       </c>
       <c r="F23" s="6">
@@ -19702,7 +19995,7 @@
           <t>فلانك</t>
         </is>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="20" t="n">
         <v>20</v>
       </c>
       <c r="F24" s="6">
@@ -19740,7 +20033,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="21" t="n">
+      <c r="E25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
@@ -19777,7 +20070,7 @@
           <t>ثوم</t>
         </is>
       </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F26" s="6">
@@ -19815,7 +20108,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="20" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="6">
@@ -19853,7 +20146,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="6" t="n">
@@ -19890,7 +20183,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E29" s="21" t="n">
+      <c r="E29" s="20" t="n">
         <v>4</v>
       </c>
       <c r="F29" s="6">
@@ -19928,7 +20221,7 @@
           <t>جلد</t>
         </is>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="E30" s="20" t="n">
         <v>10</v>
       </c>
       <c r="F30" s="6">
@@ -19966,7 +20259,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="20" t="n">
         <v>28</v>
       </c>
       <c r="F31" s="6" t="n">
@@ -20003,7 +20296,7 @@
           <t>دوبريه</t>
         </is>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="20" t="n">
         <v>10</v>
       </c>
       <c r="F32" s="6">
@@ -20041,7 +20334,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="6">
@@ -20079,7 +20372,7 @@
           <t>سعر كجم الخلطة الفرعية</t>
         </is>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="E34" s="20" t="n">
         <v>3.12</v>
       </c>
       <c r="F34" s="6">
@@ -20097,25 +20390,25 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>سجق ابوهاشم</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="22">
         <f>SUM(E21:E34)</f>
         <v/>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="23">
         <f>SUM(G21:G34)</f>
         <v/>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 98.96 كجم</t>
         </is>
@@ -20142,7 +20435,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="20" t="n">
         <v>0.4</v>
       </c>
       <c r="F37" s="6">
@@ -20180,7 +20473,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="F38" s="6">
@@ -20218,7 +20511,7 @@
           <t>طعم كفته</t>
         </is>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="6">
@@ -20256,7 +20549,7 @@
           <t>طعم شواي</t>
         </is>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="F40" s="6">
@@ -20294,7 +20587,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E41" s="21" t="n">
+      <c r="E41" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="F41" s="6">
@@ -20332,7 +20625,7 @@
           <t>خلنجان</t>
         </is>
       </c>
-      <c r="E42" s="21" t="n">
+      <c r="E42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="6">
@@ -20370,7 +20663,7 @@
           <t>فلفل اسود</t>
         </is>
       </c>
-      <c r="E43" s="21" t="n">
+      <c r="E43" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="F43" s="6">
@@ -20408,7 +20701,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E44" s="21" t="n">
+      <c r="E44" s="20" t="n">
         <v>0.05</v>
       </c>
       <c r="F44" s="6">
@@ -20446,7 +20739,7 @@
           <t>كبابه</t>
         </is>
       </c>
-      <c r="E45" s="21" t="n">
+      <c r="E45" s="20" t="n">
         <v>0.04</v>
       </c>
       <c r="F45" s="6">
@@ -20484,7 +20777,7 @@
           <t>قرنفل</t>
         </is>
       </c>
-      <c r="E46" s="21" t="n">
+      <c r="E46" s="20" t="n">
         <v>0.01</v>
       </c>
       <c r="F46" s="6">
@@ -20522,7 +20815,7 @@
           <t>طعم ليه</t>
         </is>
       </c>
-      <c r="E47" s="21" t="n">
+      <c r="E47" s="20" t="n">
         <v>0.05</v>
       </c>
       <c r="F47" s="6">
@@ -20560,7 +20853,7 @@
           <t>سكر</t>
         </is>
       </c>
-      <c r="E48" s="21" t="n">
+      <c r="E48" s="20" t="n">
         <v>0.025</v>
       </c>
       <c r="F48" s="6">
@@ -20598,7 +20891,7 @@
           <t>قرفه</t>
         </is>
       </c>
-      <c r="E49" s="21" t="n">
+      <c r="E49" s="20" t="n">
         <v>0.025</v>
       </c>
       <c r="F49" s="6">
@@ -20636,7 +20929,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="E50" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="6">
@@ -20674,7 +20967,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E51" s="21" t="n">
+      <c r="E51" s="20" t="n">
         <v>1.2</v>
       </c>
       <c r="F51" s="6">
@@ -20692,25 +20985,25 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>كفته ابوهاشم</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>إجمالى خلطة فرعية (توابل)</t>
         </is>
       </c>
-      <c r="E52" s="23">
+      <c r="E52" s="22">
         <f>SUM(E37:E51)</f>
         <v/>
       </c>
-      <c r="F52" s="15">
+      <c r="F52" s="14">
         <f>G52/E52</f>
         <v/>
       </c>
-      <c r="G52" s="24">
+      <c r="G52" s="23">
         <f>SUM(G37:G51)</f>
         <v/>
       </c>
@@ -20736,7 +21029,7 @@
           <t>فلانك</t>
         </is>
       </c>
-      <c r="E54" s="21" t="n">
+      <c r="E54" s="20" t="n">
         <v>20</v>
       </c>
       <c r="F54" s="6">
@@ -20774,20 +21067,20 @@
           <t>مفروم فراخ فاخر</t>
         </is>
       </c>
-      <c r="E55" s="21" t="n">
+      <c r="E55" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="F55" s="17">
-        <f>'احتساب متوسط سبتمبر'!C12</f>
+      <c r="F55" s="6">
+        <f>'احتساب متوسط سبتمبر'!I12</f>
         <v/>
       </c>
       <c r="G55" s="5">
         <f>E55*F55</f>
         <v/>
       </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -20812,7 +21105,7 @@
           <t>فلفل رومي حامي</t>
         </is>
       </c>
-      <c r="E56" s="21" t="n">
+      <c r="E56" s="20" t="n">
         <v>2.5</v>
       </c>
       <c r="F56" s="6">
@@ -20850,7 +21143,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E57" s="21" t="n">
+      <c r="E57" s="20" t="n">
         <v>9</v>
       </c>
       <c r="F57" s="6">
@@ -20888,7 +21181,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E58" s="21" t="n">
+      <c r="E58" s="20" t="n">
         <v>7.5</v>
       </c>
       <c r="F58" s="6">
@@ -20926,7 +21219,7 @@
           <t>فلفل رومي حامي</t>
         </is>
       </c>
-      <c r="E59" s="21" t="n">
+      <c r="E59" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="F59" s="6">
@@ -20964,7 +21257,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E60" s="21" t="n">
+      <c r="E60" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="6">
@@ -21002,7 +21295,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E61" s="21" t="n">
+      <c r="E61" s="20" t="n">
         <v>6</v>
       </c>
       <c r="F61" s="6">
@@ -21040,7 +21333,7 @@
           <t>صويا اوزيليت</t>
         </is>
       </c>
-      <c r="E62" s="21" t="n">
+      <c r="E62" s="20" t="n">
         <v>1.2</v>
       </c>
       <c r="F62" s="6">
@@ -21078,7 +21371,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E63" s="21" t="n">
+      <c r="E63" s="20" t="n">
         <v>15</v>
       </c>
       <c r="F63" s="6" t="n">
@@ -21115,7 +21408,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E64" s="21" t="n">
+      <c r="E64" s="20" t="n">
         <v>2.5</v>
       </c>
       <c r="F64" s="6">
@@ -21153,7 +21446,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E65" s="21" t="n">
+      <c r="E65" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F65" s="6">
@@ -21191,7 +21484,7 @@
           <t>دوبريه</t>
         </is>
       </c>
-      <c r="E66" s="21" t="n">
+      <c r="E66" s="20" t="n">
         <v>5</v>
       </c>
       <c r="F66" s="6">
@@ -21229,7 +21522,7 @@
           <t>سعر كجم الخلطة الفرعية</t>
         </is>
       </c>
-      <c r="E67" s="21" t="n">
+      <c r="E67" s="20" t="n">
         <v>2.6</v>
       </c>
       <c r="F67" s="6">
@@ -21247,25 +21540,25 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="inlineStr">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>كفته ابوهاشم</t>
         </is>
       </c>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E68" s="23">
+      <c r="E68" s="22">
         <f>SUM(E54:E67)</f>
         <v/>
       </c>
-      <c r="G68" s="24">
+      <c r="G68" s="23">
         <f>SUM(G54:G67)</f>
         <v/>
       </c>
-      <c r="H68" s="22" t="inlineStr">
+      <c r="H68" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 78.5 كجم</t>
         </is>
@@ -21292,7 +21585,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E70" s="21" t="n">
+      <c r="E70" s="20" t="n">
         <v>0.25</v>
       </c>
       <c r="F70" s="6">
@@ -21330,7 +21623,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E71" s="21" t="n">
+      <c r="E71" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="F71" s="6">
@@ -21368,7 +21661,7 @@
           <t>طعم برجر</t>
         </is>
       </c>
-      <c r="E72" s="21" t="n">
+      <c r="E72" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="F72" s="6">
@@ -21406,7 +21699,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E73" s="21" t="n">
+      <c r="E73" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
@@ -21443,7 +21736,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E74" s="21" t="n">
+      <c r="E74" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F74" s="6">
@@ -21481,7 +21774,7 @@
           <t>قرفه</t>
         </is>
       </c>
-      <c r="E75" s="21" t="n">
+      <c r="E75" s="20" t="n">
         <v>0.05</v>
       </c>
       <c r="F75" s="6">
@@ -21519,7 +21812,7 @@
           <t>فلفل اسود</t>
         </is>
       </c>
-      <c r="E76" s="21" t="n">
+      <c r="E76" s="20" t="n">
         <v>0.25</v>
       </c>
       <c r="F76" s="6">
@@ -21557,7 +21850,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E77" s="21" t="n">
+      <c r="E77" s="20" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="F77" s="6">
@@ -21595,7 +21888,7 @@
           <t>كبابه</t>
         </is>
       </c>
-      <c r="E78" s="21" t="n">
+      <c r="E78" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="6">
@@ -21633,7 +21926,7 @@
           <t>قرنفل</t>
         </is>
       </c>
-      <c r="E79" s="21" t="n">
+      <c r="E79" s="20" t="n">
         <v>0.025</v>
       </c>
       <c r="F79" s="6">
@@ -21671,7 +21964,7 @@
           <t>زعتر</t>
         </is>
       </c>
-      <c r="E80" s="21" t="n">
+      <c r="E80" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="6">
@@ -21709,7 +22002,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E81" s="21" t="n">
+      <c r="E81" s="20" t="n">
         <v>0.01</v>
       </c>
       <c r="F81" s="6">
@@ -21747,7 +22040,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E82" s="21" t="n">
+      <c r="E82" s="20" t="n">
         <v>0.8</v>
       </c>
       <c r="F82" s="6">
@@ -21765,25 +22058,25 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="inlineStr">
+      <c r="A83" s="21" t="inlineStr">
         <is>
           <t>برجر ابوهاشم</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>إجمالى خلطة فرعية (توابل)</t>
         </is>
       </c>
-      <c r="E83" s="23">
+      <c r="E83" s="22">
         <f>SUM(E70:E82)</f>
         <v/>
       </c>
-      <c r="F83" s="15">
+      <c r="F83" s="14">
         <f>G83/E83</f>
         <v/>
       </c>
-      <c r="G83" s="24">
+      <c r="G83" s="23">
         <f>SUM(G70:G82)</f>
         <v/>
       </c>
@@ -21809,7 +22102,7 @@
           <t>@مجمع اللحوم الهندى</t>
         </is>
       </c>
-      <c r="E85" s="21" t="n">
+      <c r="E85" s="20" t="n">
         <v>12</v>
       </c>
       <c r="F85" s="6">
@@ -21847,7 +22140,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E86" s="21" t="n">
+      <c r="E86" s="20" t="n">
         <v>5</v>
       </c>
       <c r="F86" s="6">
@@ -21885,7 +22178,7 @@
           <t>دوبريه</t>
         </is>
       </c>
-      <c r="E87" s="21" t="n">
+      <c r="E87" s="20" t="n">
         <v>6</v>
       </c>
       <c r="F87" s="6">
@@ -21923,7 +22216,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E88" s="21" t="n">
+      <c r="E88" s="20" t="n">
         <v>6</v>
       </c>
       <c r="F88" s="6">
@@ -21961,7 +22254,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E89" s="21" t="n">
+      <c r="E89" s="20" t="n">
         <v>4</v>
       </c>
       <c r="F89" s="6">
@@ -21999,7 +22292,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E90" s="21" t="n">
+      <c r="E90" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="6">
@@ -22037,7 +22330,7 @@
           <t>ثوم</t>
         </is>
       </c>
-      <c r="E91" s="21" t="n">
+      <c r="E91" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F91" s="6">
@@ -22075,7 +22368,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E92" s="21" t="n">
+      <c r="E92" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F92" s="6">
@@ -22113,7 +22406,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E93" s="21" t="n">
+      <c r="E93" s="20" t="n">
         <v>4</v>
       </c>
       <c r="F93" s="6">
@@ -22151,7 +22444,7 @@
           <t>صويا اوزيليت</t>
         </is>
       </c>
-      <c r="E94" s="21" t="n">
+      <c r="E94" s="20" t="n">
         <v>0.25</v>
       </c>
       <c r="F94" s="6">
@@ -22189,20 +22482,20 @@
           <t>مفروم فراخ شعبي</t>
         </is>
       </c>
-      <c r="E95" s="21" t="n">
+      <c r="E95" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="F95" s="17">
-        <f>'احتساب متوسط سبتمبر'!C8</f>
+      <c r="F95" s="6">
+        <f>'احتساب متوسط سبتمبر'!I8</f>
         <v/>
       </c>
       <c r="G95" s="5">
         <f>E95*F95</f>
         <v/>
       </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -22227,7 +22520,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E96" s="21" t="n">
+      <c r="E96" s="20" t="n">
         <v>14</v>
       </c>
       <c r="F96" s="6" t="n">
@@ -22264,7 +22557,7 @@
           <t>سعر كجم الخلطة الفرعية</t>
         </is>
       </c>
-      <c r="E97" s="21" t="n">
+      <c r="E97" s="20" t="n">
         <v>1.905</v>
       </c>
       <c r="F97" s="6">
@@ -22282,25 +22575,25 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="inlineStr">
+      <c r="A98" s="21" t="inlineStr">
         <is>
           <t>برجر ابوهاشم</t>
         </is>
       </c>
-      <c r="B98" s="14" t="inlineStr">
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E98" s="23">
+      <c r="E98" s="22">
         <f>SUM(E85:E97)</f>
         <v/>
       </c>
-      <c r="G98" s="24">
+      <c r="G98" s="23">
         <f>SUM(G85:G97)</f>
         <v/>
       </c>
-      <c r="H98" s="22" t="inlineStr">
+      <c r="H98" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 62.655 كجم</t>
         </is>
@@ -22327,20 +22620,20 @@
           <t>مفروم فراخ شعبي</t>
         </is>
       </c>
-      <c r="E100" s="21" t="n">
+      <c r="E100" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="F100" s="17">
-        <f>'احتساب متوسط سبتمبر'!C8</f>
+      <c r="F100" s="6">
+        <f>'احتساب متوسط سبتمبر'!I8</f>
         <v/>
       </c>
       <c r="G100" s="5">
         <f>E100*F100</f>
         <v/>
       </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -22365,7 +22658,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E101" s="21" t="n">
+      <c r="E101" s="20" t="n">
         <v>28</v>
       </c>
       <c r="F101" s="6">
@@ -22403,7 +22696,7 @@
           <t>— (سعر ثابت بالوصفة)</t>
         </is>
       </c>
-      <c r="E102" s="21" t="n">
+      <c r="E102" s="20" t="n">
         <v>25</v>
       </c>
       <c r="F102" s="6" t="n">
@@ -22440,7 +22733,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E103" s="21" t="n">
+      <c r="E103" s="20" t="n">
         <v>43</v>
       </c>
       <c r="F103" s="6">
@@ -22478,7 +22771,7 @@
           <t>فلفل رومي حامي</t>
         </is>
       </c>
-      <c r="E104" s="21" t="n">
+      <c r="E104" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F104" s="6">
@@ -22516,7 +22809,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E105" s="21" t="n">
+      <c r="E105" s="20" t="n">
         <v>28</v>
       </c>
       <c r="F105" s="6">
@@ -22554,7 +22847,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E106" s="21" t="n">
+      <c r="E106" s="20" t="n">
         <v>24</v>
       </c>
       <c r="F106" s="6">
@@ -22592,7 +22885,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E107" s="21" t="n">
+      <c r="E107" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
@@ -22629,7 +22922,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E108" s="21" t="n">
+      <c r="E108" s="20" t="n">
         <v>25</v>
       </c>
       <c r="F108" s="6">
@@ -22667,7 +22960,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E109" s="21" t="n">
+      <c r="E109" s="20" t="n">
         <v>26</v>
       </c>
       <c r="F109" s="6">
@@ -22705,7 +22998,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E110" s="21" t="n">
+      <c r="E110" s="20" t="n">
         <v>99</v>
       </c>
       <c r="F110" s="6" t="n">
@@ -22742,7 +23035,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E111" s="21" t="n">
+      <c r="E111" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F111" s="6">
@@ -22780,7 +23073,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E112" s="21" t="n">
+      <c r="E112" s="20" t="n">
         <v>0.09</v>
       </c>
       <c r="F112" s="6">
@@ -22818,7 +23111,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E113" s="21" t="n">
+      <c r="E113" s="20" t="n">
         <v>0.6</v>
       </c>
       <c r="F113" s="6">
@@ -22856,7 +23149,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E114" s="21" t="n">
+      <c r="E114" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F114" s="6">
@@ -22894,7 +23187,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E115" s="21" t="n">
+      <c r="E115" s="20" t="n">
         <v>6.8</v>
       </c>
       <c r="F115" s="6">
@@ -22932,7 +23225,7 @@
           <t>حبهان</t>
         </is>
       </c>
-      <c r="E116" s="21" t="n">
+      <c r="E116" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="F116" s="6">
@@ -22970,7 +23263,7 @@
           <t>طعم كفته</t>
         </is>
       </c>
-      <c r="E117" s="21" t="n">
+      <c r="E117" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F117" s="6">
@@ -23008,7 +23301,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E118" s="21" t="n">
+      <c r="E118" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F118" s="6">
@@ -23046,7 +23339,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E119" s="21" t="n">
+      <c r="E119" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F119" s="6">
@@ -23084,7 +23377,7 @@
           <t>جنزبيل</t>
         </is>
       </c>
-      <c r="E120" s="21" t="n">
+      <c r="E120" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="F120" s="6">
@@ -23122,7 +23415,7 @@
           <t>طعم ليه</t>
         </is>
       </c>
-      <c r="E121" s="21" t="n">
+      <c r="E121" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F121" s="6">
@@ -23160,7 +23453,7 @@
           <t>بابريكا</t>
         </is>
       </c>
-      <c r="E122" s="21" t="n">
+      <c r="E122" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F122" s="6">
@@ -23178,25 +23471,25 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="22" t="inlineStr">
+      <c r="A123" s="21" t="inlineStr">
         <is>
           <t>برجر اسبشيال</t>
         </is>
       </c>
-      <c r="B123" s="14" t="inlineStr">
+      <c r="B123" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E123" s="23">
+      <c r="E123" s="22">
         <f>SUM(E100:E122)</f>
         <v/>
       </c>
-      <c r="G123" s="24">
+      <c r="G123" s="23">
         <f>SUM(G100:G122)</f>
         <v/>
       </c>
-      <c r="H123" s="22" t="inlineStr">
+      <c r="H123" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 394.39 كجم</t>
         </is>
@@ -23223,20 +23516,20 @@
           <t>مفروم فراخ شعبي</t>
         </is>
       </c>
-      <c r="E125" s="21" t="n">
+      <c r="E125" s="20" t="n">
         <v>105</v>
       </c>
-      <c r="F125" s="17">
-        <f>'احتساب متوسط سبتمبر'!C8</f>
+      <c r="F125" s="6">
+        <f>'احتساب متوسط سبتمبر'!I8</f>
         <v/>
       </c>
       <c r="G125" s="5">
         <f>E125*F125</f>
         <v/>
       </c>
-      <c r="H125" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23554,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E126" s="21" t="n">
+      <c r="E126" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="6">
@@ -23299,7 +23592,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E127" s="21" t="n">
+      <c r="E127" s="20" t="n">
         <v>10.5</v>
       </c>
       <c r="F127" s="6">
@@ -23337,7 +23630,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E128" s="21" t="n">
+      <c r="E128" s="20" t="n">
         <v>48</v>
       </c>
       <c r="F128" s="6" t="n">
@@ -23374,7 +23667,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E129" s="21" t="n">
+      <c r="E129" s="20" t="n">
         <v>21.75</v>
       </c>
       <c r="F129" s="6">
@@ -23412,7 +23705,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E130" s="21" t="n">
+      <c r="E130" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="6">
@@ -23450,7 +23743,7 @@
           <t>جلد</t>
         </is>
       </c>
-      <c r="E131" s="21" t="n">
+      <c r="E131" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="6">
@@ -23488,7 +23781,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E132" s="21" t="n">
+      <c r="E132" s="20" t="n">
         <v>7.5</v>
       </c>
       <c r="F132" s="6">
@@ -23526,7 +23819,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E133" s="21" t="n">
+      <c r="E133" s="20" t="n">
         <v>19.5</v>
       </c>
       <c r="F133" s="6">
@@ -23564,7 +23857,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E134" s="21" t="n">
+      <c r="E134" s="20" t="n">
         <v>4.2</v>
       </c>
       <c r="F134" s="6">
@@ -23602,7 +23895,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E135" s="21" t="n">
+      <c r="E135" s="20" t="n">
         <v>1.5</v>
       </c>
       <c r="F135" s="6">
@@ -23640,7 +23933,7 @@
           <t>لورا</t>
         </is>
       </c>
-      <c r="E136" s="21" t="n">
+      <c r="E136" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="6">
@@ -23678,7 +23971,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E137" s="21" t="n">
+      <c r="E137" s="20" t="n">
         <v>0.75</v>
       </c>
       <c r="F137" s="6">
@@ -23716,7 +24009,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E138" s="21" t="n">
+      <c r="E138" s="20" t="n">
         <v>1.5</v>
       </c>
       <c r="F138" s="6">
@@ -23754,7 +24047,7 @@
           <t>فلفل اسود</t>
         </is>
       </c>
-      <c r="E139" s="21" t="n">
+      <c r="E139" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="6">
@@ -23792,7 +24085,7 @@
           <t>خلنجان</t>
         </is>
       </c>
-      <c r="E140" s="21" t="n">
+      <c r="E140" s="20" t="n">
         <v>0.75</v>
       </c>
       <c r="F140" s="6">
@@ -23830,7 +24123,7 @@
           <t>ثوم</t>
         </is>
       </c>
-      <c r="E141" s="21" t="n">
+      <c r="E141" s="20" t="n">
         <v>4.5</v>
       </c>
       <c r="F141" s="6">
@@ -23868,7 +24161,7 @@
           <t>زعتر</t>
         </is>
       </c>
-      <c r="E142" s="21" t="n">
+      <c r="E142" s="20" t="n">
         <v>0.38</v>
       </c>
       <c r="F142" s="6">
@@ -23906,7 +24199,7 @@
           <t>ينسون</t>
         </is>
       </c>
-      <c r="E143" s="21" t="n">
+      <c r="E143" s="20" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="F143" s="6">
@@ -23944,7 +24237,7 @@
           <t>قرفه</t>
         </is>
       </c>
-      <c r="E144" s="21" t="n">
+      <c r="E144" s="20" t="n">
         <v>0.6</v>
       </c>
       <c r="F144" s="6">
@@ -23982,7 +24275,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E145" s="21" t="n">
+      <c r="E145" s="20" t="n">
         <v>1.2</v>
       </c>
       <c r="F145" s="6">
@@ -24020,7 +24313,7 @@
           <t>طعم سجق بودر</t>
         </is>
       </c>
-      <c r="E146" s="21" t="n">
+      <c r="E146" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="F146" s="6">
@@ -24058,7 +24351,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E147" s="21" t="n">
+      <c r="E147" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F147" s="6">
@@ -24096,7 +24389,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E148" s="21" t="n">
+      <c r="E148" s="20" t="n">
         <v>0.04</v>
       </c>
       <c r="F148" s="6">
@@ -24114,25 +24407,25 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="22" t="inlineStr">
+      <c r="A149" s="21" t="inlineStr">
         <is>
           <t>سجق اسبشيال</t>
         </is>
       </c>
-      <c r="B149" s="14" t="inlineStr">
+      <c r="B149" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E149" s="23">
+      <c r="E149" s="22">
         <f>SUM(E125:E148)</f>
         <v/>
       </c>
-      <c r="G149" s="24">
+      <c r="G149" s="23">
         <f>SUM(G125:G148)</f>
         <v/>
       </c>
-      <c r="H149" s="22" t="inlineStr">
+      <c r="H149" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 228.659 كجم</t>
         </is>
@@ -24159,20 +24452,20 @@
           <t>مفروم فراخ شعبي</t>
         </is>
       </c>
-      <c r="E151" s="21" t="n">
+      <c r="E151" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="F151" s="17">
-        <f>'احتساب متوسط سبتمبر'!C8</f>
+      <c r="F151" s="6">
+        <f>'احتساب متوسط سبتمبر'!I8</f>
         <v/>
       </c>
       <c r="G151" s="5">
         <f>E151*F151</f>
         <v/>
       </c>
-      <c r="H151" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -24197,7 +24490,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E152" s="21" t="n">
+      <c r="E152" s="20" t="n">
         <v>60</v>
       </c>
       <c r="F152" s="6">
@@ -24235,7 +24528,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E153" s="21" t="n">
+      <c r="E153" s="20" t="n">
         <v>15</v>
       </c>
       <c r="F153" s="6" t="n">
@@ -24272,7 +24565,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E154" s="21" t="n">
+      <c r="E154" s="20" t="n">
         <v>27</v>
       </c>
       <c r="F154" s="6">
@@ -24310,7 +24603,7 @@
           <t>— (سعر ثابت بالوصفة)</t>
         </is>
       </c>
-      <c r="E155" s="21" t="n">
+      <c r="E155" s="20" t="n">
         <v>15</v>
       </c>
       <c r="F155" s="6" t="n">
@@ -24347,7 +24640,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E156" s="21" t="n">
+      <c r="E156" s="20" t="n">
         <v>15</v>
       </c>
       <c r="F156" s="6">
@@ -24385,7 +24678,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E157" s="21" t="n">
+      <c r="E157" s="20" t="n">
         <v>15</v>
       </c>
       <c r="F157" s="6">
@@ -24423,7 +24716,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E158" s="21" t="n">
+      <c r="E158" s="20" t="n">
         <v>30</v>
       </c>
       <c r="F158" s="6">
@@ -24461,7 +24754,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E159" s="21" t="n">
+      <c r="E159" s="20" t="n">
         <v>19.5</v>
       </c>
       <c r="F159" s="6">
@@ -24499,7 +24792,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E160" s="21" t="n">
+      <c r="E160" s="20" t="n">
         <v>60</v>
       </c>
       <c r="F160" s="6" t="n">
@@ -24536,7 +24829,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E161" s="21" t="n">
+      <c r="E161" s="20" t="n">
         <v>1.2</v>
       </c>
       <c r="F161" s="6">
@@ -24574,7 +24867,7 @@
           <t>صويا اوزيليت</t>
         </is>
       </c>
-      <c r="E162" s="21" t="n">
+      <c r="E162" s="20" t="n">
         <v>4.5</v>
       </c>
       <c r="F162" s="6">
@@ -24612,7 +24905,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E163" s="21" t="n">
+      <c r="E163" s="20" t="n">
         <v>0.75</v>
       </c>
       <c r="F163" s="6">
@@ -24650,7 +24943,7 @@
           <t>كبابه</t>
         </is>
       </c>
-      <c r="E164" s="21" t="n">
+      <c r="E164" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F164" s="6">
@@ -24688,7 +24981,7 @@
           <t>قرنفل</t>
         </is>
       </c>
-      <c r="E165" s="21" t="n">
+      <c r="E165" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F165" s="6">
@@ -24726,7 +25019,7 @@
           <t>قرفه</t>
         </is>
       </c>
-      <c r="E166" s="21" t="n">
+      <c r="E166" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F166" s="6">
@@ -24764,7 +25057,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E167" s="21" t="n">
+      <c r="E167" s="20" t="n">
         <v>1.8</v>
       </c>
       <c r="F167" s="6">
@@ -24802,7 +25095,7 @@
           <t>ينسون</t>
         </is>
       </c>
-      <c r="E168" s="21" t="n">
+      <c r="E168" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F168" s="6">
@@ -24840,7 +25133,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E169" s="21" t="n">
+      <c r="E169" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F169" s="6">
@@ -24878,7 +25171,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E170" s="21" t="n">
+      <c r="E170" s="20" t="n">
         <v>5.1</v>
       </c>
       <c r="F170" s="6">
@@ -24916,7 +25209,7 @@
           <t>فلفل اسود</t>
         </is>
       </c>
-      <c r="E171" s="21" t="n">
+      <c r="E171" s="20" t="n">
         <v>1.5</v>
       </c>
       <c r="F171" s="6">
@@ -24954,7 +25247,7 @@
           <t>حبهان</t>
         </is>
       </c>
-      <c r="E172" s="21" t="n">
+      <c r="E172" s="20" t="n">
         <v>0.12</v>
       </c>
       <c r="F172" s="6">
@@ -24992,7 +25285,7 @@
           <t>لورا</t>
         </is>
       </c>
-      <c r="E173" s="21" t="n">
+      <c r="E173" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="F173" s="6">
@@ -25030,7 +25323,7 @@
           <t>طعم شواي</t>
         </is>
       </c>
-      <c r="E174" s="21" t="n">
+      <c r="E174" s="20" t="n">
         <v>0.75</v>
       </c>
       <c r="F174" s="6">
@@ -25068,7 +25361,7 @@
           <t>طعم كفته</t>
         </is>
       </c>
-      <c r="E175" s="21" t="n">
+      <c r="E175" s="20" t="n">
         <v>0.75</v>
       </c>
       <c r="F175" s="6">
@@ -25106,7 +25399,7 @@
           <t>طعم ليه</t>
         </is>
       </c>
-      <c r="E176" s="21" t="n">
+      <c r="E176" s="20" t="n">
         <v>1.2</v>
       </c>
       <c r="F176" s="6">
@@ -25144,7 +25437,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E177" s="21" t="n">
+      <c r="E177" s="20" t="n">
         <v>0.75</v>
       </c>
       <c r="F177" s="6">
@@ -25182,7 +25475,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E178" s="21" t="n">
+      <c r="E178" s="20" t="n">
         <v>0.03</v>
       </c>
       <c r="F178" s="6">
@@ -25200,25 +25493,25 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="22" t="inlineStr">
+      <c r="A179" s="21" t="inlineStr">
         <is>
           <t>كفته اسبشيال</t>
         </is>
       </c>
-      <c r="B179" s="14" t="inlineStr">
+      <c r="B179" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E179" s="23">
+      <c r="E179" s="22">
         <f>SUM(E151:E178)</f>
         <v/>
       </c>
-      <c r="G179" s="24">
+      <c r="G179" s="23">
         <f>SUM(G151:G178)</f>
         <v/>
       </c>
-      <c r="H179" s="22" t="inlineStr">
+      <c r="H179" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 365.4 كجم</t>
         </is>
@@ -25245,20 +25538,20 @@
           <t>مفروم فراخ شعبي</t>
         </is>
       </c>
-      <c r="E181" s="21" t="n">
+      <c r="E181" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="F181" s="17">
-        <f>'احتساب متوسط سبتمبر'!C8</f>
+      <c r="F181" s="6">
+        <f>'احتساب متوسط سبتمبر'!I8</f>
         <v/>
       </c>
       <c r="G181" s="5">
         <f>E181*F181</f>
         <v/>
       </c>
-      <c r="H181" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -25283,7 +25576,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E182" s="21" t="n">
+      <c r="E182" s="20" t="n">
         <v>27</v>
       </c>
       <c r="F182" s="6">
@@ -25321,7 +25614,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E183" s="21" t="n">
+      <c r="E183" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F183" s="6" t="n">
@@ -25358,7 +25651,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E184" s="21" t="n">
+      <c r="E184" s="20" t="n">
         <v>15</v>
       </c>
       <c r="F184" s="6">
@@ -25396,7 +25689,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E185" s="21" t="n">
+      <c r="E185" s="20" t="n">
         <v>22.5</v>
       </c>
       <c r="F185" s="6">
@@ -25434,7 +25727,7 @@
           <t>جلد</t>
         </is>
       </c>
-      <c r="E186" s="21" t="n">
+      <c r="E186" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F186" s="6">
@@ -25472,7 +25765,7 @@
           <t>ثوم</t>
         </is>
       </c>
-      <c r="E187" s="21" t="n">
+      <c r="E187" s="20" t="n">
         <v>7.5</v>
       </c>
       <c r="F187" s="6">
@@ -25510,7 +25803,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E188" s="21" t="n">
+      <c r="E188" s="20" t="n">
         <v>21</v>
       </c>
       <c r="F188" s="6">
@@ -25548,7 +25841,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E189" s="21" t="n">
+      <c r="E189" s="20" t="n">
         <v>67.5</v>
       </c>
       <c r="F189" s="6" t="n">
@@ -25585,7 +25878,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E190" s="21" t="n">
+      <c r="E190" s="20" t="n">
         <v>0.9</v>
       </c>
       <c r="F190" s="6">
@@ -25623,7 +25916,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E191" s="21" t="n">
+      <c r="E191" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F191" s="6">
@@ -25661,7 +25954,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E192" s="21" t="n">
+      <c r="E192" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F192" s="6">
@@ -25699,7 +25992,7 @@
           <t>كبابه</t>
         </is>
       </c>
-      <c r="E193" s="21" t="n">
+      <c r="E193" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F193" s="6">
@@ -25737,7 +26030,7 @@
           <t>قرنفل</t>
         </is>
       </c>
-      <c r="E194" s="21" t="n">
+      <c r="E194" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F194" s="6">
@@ -25775,7 +26068,7 @@
           <t>قرفه</t>
         </is>
       </c>
-      <c r="E195" s="21" t="n">
+      <c r="E195" s="20" t="n">
         <v>0.24</v>
       </c>
       <c r="F195" s="6">
@@ -25813,7 +26106,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E196" s="21" t="n">
+      <c r="E196" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F196" s="6">
@@ -25851,7 +26144,7 @@
           <t>ينسون</t>
         </is>
       </c>
-      <c r="E197" s="21" t="n">
+      <c r="E197" s="20" t="n">
         <v>0.12</v>
       </c>
       <c r="F197" s="6">
@@ -25889,7 +26182,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E198" s="21" t="n">
+      <c r="E198" s="20" t="n">
         <v>0.42</v>
       </c>
       <c r="F198" s="6">
@@ -25927,7 +26220,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E199" s="21" t="n">
+      <c r="E199" s="20" t="n">
         <v>4.2</v>
       </c>
       <c r="F199" s="6">
@@ -25965,7 +26258,7 @@
           <t>بابريكا</t>
         </is>
       </c>
-      <c r="E200" s="21" t="n">
+      <c r="E200" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="F200" s="6">
@@ -26003,7 +26296,7 @@
           <t>كمون</t>
         </is>
       </c>
-      <c r="E201" s="21" t="n">
+      <c r="E201" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F201" s="6">
@@ -26041,7 +26334,7 @@
           <t>لورا</t>
         </is>
       </c>
-      <c r="E202" s="21" t="n">
+      <c r="E202" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F202" s="6">
@@ -26079,7 +26372,7 @@
           <t>طعم ليه</t>
         </is>
       </c>
-      <c r="E203" s="21" t="n">
+      <c r="E203" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F203" s="6">
@@ -26117,7 +26410,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E204" s="21" t="n">
+      <c r="E204" s="20" t="n">
         <v>0.03</v>
       </c>
       <c r="F204" s="6">
@@ -26155,7 +26448,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E205" s="21" t="n">
+      <c r="E205" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="F205" s="6">
@@ -26173,25 +26466,25 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="22" t="inlineStr">
+      <c r="A206" s="21" t="inlineStr">
         <is>
           <t>سجق الهنا</t>
         </is>
       </c>
-      <c r="B206" s="14" t="inlineStr">
+      <c r="B206" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E206" s="23">
+      <c r="E206" s="22">
         <f>SUM(E181:E205)</f>
         <v/>
       </c>
-      <c r="G206" s="24">
+      <c r="G206" s="23">
         <f>SUM(G181:G205)</f>
         <v/>
       </c>
-      <c r="H206" s="22" t="inlineStr">
+      <c r="H206" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 227.26 كجم</t>
         </is>
@@ -26218,20 +26511,20 @@
           <t>مفروم فراخ شعبي</t>
         </is>
       </c>
-      <c r="E208" s="21" t="n">
+      <c r="E208" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="F208" s="17">
-        <f>'احتساب متوسط سبتمبر'!C8</f>
+      <c r="F208" s="6">
+        <f>'احتساب متوسط سبتمبر'!I8</f>
         <v/>
       </c>
       <c r="G208" s="5">
         <f>E208*F208</f>
         <v/>
       </c>
-      <c r="H208" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -26256,7 +26549,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E209" s="21" t="n">
+      <c r="E209" s="20" t="n">
         <v>40</v>
       </c>
       <c r="F209" s="6">
@@ -26294,7 +26587,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E210" s="21" t="n">
+      <c r="E210" s="20" t="n">
         <v>20</v>
       </c>
       <c r="F210" s="6">
@@ -26332,7 +26625,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E211" s="21" t="n">
+      <c r="E211" s="20" t="n">
         <v>116</v>
       </c>
       <c r="F211" s="6" t="n">
@@ -26369,7 +26662,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E212" s="21" t="n">
+      <c r="E212" s="20" t="n">
         <v>44</v>
       </c>
       <c r="F212" s="6">
@@ -26407,7 +26700,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E213" s="21" t="n">
+      <c r="E213" s="20" t="n">
         <v>20</v>
       </c>
       <c r="F213" s="6">
@@ -26445,7 +26738,7 @@
           <t>جلد</t>
         </is>
       </c>
-      <c r="E214" s="21" t="n">
+      <c r="E214" s="20" t="n">
         <v>20</v>
       </c>
       <c r="F214" s="6">
@@ -26483,7 +26776,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E215" s="21" t="n">
+      <c r="E215" s="20" t="n">
         <v>20</v>
       </c>
       <c r="F215" s="6">
@@ -26521,7 +26814,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E216" s="21" t="n">
+      <c r="E216" s="20" t="n">
         <v>36</v>
       </c>
       <c r="F216" s="6">
@@ -26559,7 +26852,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E217" s="21" t="n">
+      <c r="E217" s="20" t="n">
         <v>6.4</v>
       </c>
       <c r="F217" s="6">
@@ -26597,7 +26890,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E218" s="21" t="n">
+      <c r="E218" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F218" s="6">
@@ -26635,7 +26928,7 @@
           <t>لورا</t>
         </is>
       </c>
-      <c r="E219" s="21" t="n">
+      <c r="E219" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="F219" s="6">
@@ -26673,7 +26966,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E220" s="21" t="n">
+      <c r="E220" s="20" t="n">
         <v>0.4</v>
       </c>
       <c r="F220" s="6">
@@ -26711,7 +27004,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E221" s="21" t="n">
+      <c r="E221" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F221" s="6">
@@ -26749,7 +27042,7 @@
           <t>قرفه</t>
         </is>
       </c>
-      <c r="E222" s="21" t="n">
+      <c r="E222" s="20" t="n">
         <v>0.6</v>
       </c>
       <c r="F222" s="6">
@@ -26787,7 +27080,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E223" s="21" t="n">
+      <c r="E223" s="20" t="n">
         <v>0.8</v>
       </c>
       <c r="F223" s="6">
@@ -26825,7 +27118,7 @@
           <t>طعم شواي</t>
         </is>
       </c>
-      <c r="E224" s="21" t="n">
+      <c r="E224" s="20" t="n">
         <v>0.8</v>
       </c>
       <c r="F224" s="6">
@@ -26863,7 +27156,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E225" s="21" t="n">
+      <c r="E225" s="20" t="n">
         <v>0.8</v>
       </c>
       <c r="F225" s="6">
@@ -26901,7 +27194,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E226" s="21" t="n">
+      <c r="E226" s="20" t="n">
         <v>0.09</v>
       </c>
       <c r="F226" s="6">
@@ -26919,25 +27212,25 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="22" t="inlineStr">
+      <c r="A227" s="21" t="inlineStr">
         <is>
           <t>برجر الهنا</t>
         </is>
       </c>
-      <c r="B227" s="14" t="inlineStr">
+      <c r="B227" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E227" s="23">
+      <c r="E227" s="22">
         <f>SUM(E208:E226)</f>
         <v/>
       </c>
-      <c r="G227" s="24">
+      <c r="G227" s="23">
         <f>SUM(G208:G226)</f>
         <v/>
       </c>
-      <c r="H227" s="22" t="inlineStr">
+      <c r="H227" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 430.09 كجم</t>
         </is>
@@ -26964,20 +27257,20 @@
           <t>مفروم فراخ شعبي</t>
         </is>
       </c>
-      <c r="E229" s="21" t="n">
+      <c r="E229" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="F229" s="17">
-        <f>'احتساب متوسط سبتمبر'!C8</f>
+      <c r="F229" s="6">
+        <f>'احتساب متوسط سبتمبر'!I8</f>
         <v/>
       </c>
       <c r="G229" s="5">
         <f>E229*F229</f>
         <v/>
       </c>
-      <c r="H229" s="10" t="inlineStr">
-        <is>
-          <t>مؤقت: سعر أغسطس لحين حسم فاتورة الفراخ المفرومة</t>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>مطابقة سعر يونيه بالوصفة مع سعر الصنف بالجرد</t>
         </is>
       </c>
     </row>
@@ -27002,7 +27295,7 @@
           <t>دهن بلدي</t>
         </is>
       </c>
-      <c r="E230" s="21" t="n">
+      <c r="E230" s="20" t="n">
         <v>28</v>
       </c>
       <c r="F230" s="6">
@@ -27040,7 +27333,7 @@
           <t>— (سعر ثابت بالوصفة)</t>
         </is>
       </c>
-      <c r="E231" s="21" t="n">
+      <c r="E231" s="20" t="n">
         <v>25</v>
       </c>
       <c r="F231" s="6" t="n">
@@ -27077,7 +27370,7 @@
           <t>صويا لحمه</t>
         </is>
       </c>
-      <c r="E232" s="21" t="n">
+      <c r="E232" s="20" t="n">
         <v>43</v>
       </c>
       <c r="F232" s="6">
@@ -27115,7 +27408,7 @@
           <t>فلفل رومي حامي</t>
         </is>
       </c>
-      <c r="E233" s="21" t="n">
+      <c r="E233" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F233" s="6">
@@ -27153,7 +27446,7 @@
           <t>برغل</t>
         </is>
       </c>
-      <c r="E234" s="21" t="n">
+      <c r="E234" s="20" t="n">
         <v>28</v>
       </c>
       <c r="F234" s="6">
@@ -27191,7 +27484,7 @@
           <t>نشا</t>
         </is>
       </c>
-      <c r="E235" s="21" t="n">
+      <c r="E235" s="20" t="n">
         <v>24</v>
       </c>
       <c r="F235" s="6">
@@ -27229,7 +27522,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E236" s="21" t="n">
+      <c r="E236" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F236" s="6" t="n">
@@ -27266,7 +27559,7 @@
           <t>بصل</t>
         </is>
       </c>
-      <c r="E237" s="21" t="n">
+      <c r="E237" s="20" t="n">
         <v>25</v>
       </c>
       <c r="F237" s="6">
@@ -27304,7 +27597,7 @@
           <t>صميد</t>
         </is>
       </c>
-      <c r="E238" s="21" t="n">
+      <c r="E238" s="20" t="n">
         <v>26</v>
       </c>
       <c r="F238" s="6">
@@ -27342,7 +27635,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E239" s="21" t="n">
+      <c r="E239" s="20" t="n">
         <v>99</v>
       </c>
       <c r="F239" s="6" t="n">
@@ -27379,7 +27672,7 @@
           <t>جلتومات</t>
         </is>
       </c>
-      <c r="E240" s="21" t="n">
+      <c r="E240" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F240" s="6">
@@ -27417,7 +27710,7 @@
           <t>لون طبيعي</t>
         </is>
       </c>
-      <c r="E241" s="21" t="n">
+      <c r="E241" s="20" t="n">
         <v>0.09</v>
       </c>
       <c r="F241" s="6">
@@ -27455,7 +27748,7 @@
           <t>كزبره</t>
         </is>
       </c>
-      <c r="E242" s="21" t="n">
+      <c r="E242" s="20" t="n">
         <v>0.6</v>
       </c>
       <c r="F242" s="6">
@@ -27493,7 +27786,7 @@
           <t>شطه</t>
         </is>
       </c>
-      <c r="E243" s="21" t="n">
+      <c r="E243" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F243" s="6">
@@ -27531,7 +27824,7 @@
           <t>الملح</t>
         </is>
       </c>
-      <c r="E244" s="21" t="n">
+      <c r="E244" s="20" t="n">
         <v>6.8</v>
       </c>
       <c r="F244" s="6">
@@ -27569,7 +27862,7 @@
           <t>حبهان</t>
         </is>
       </c>
-      <c r="E245" s="21" t="n">
+      <c r="E245" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="F245" s="6">
@@ -27607,7 +27900,7 @@
           <t>طعم كفته</t>
         </is>
       </c>
-      <c r="E246" s="21" t="n">
+      <c r="E246" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F246" s="6">
@@ -27645,7 +27938,7 @@
           <t>طعم بيف</t>
         </is>
       </c>
-      <c r="E247" s="21" t="n">
+      <c r="E247" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F247" s="6">
@@ -27683,7 +27976,7 @@
           <t>فوسفات</t>
         </is>
       </c>
-      <c r="E248" s="21" t="n">
+      <c r="E248" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F248" s="6">
@@ -27721,7 +28014,7 @@
           <t>جنزبيل</t>
         </is>
       </c>
-      <c r="E249" s="21" t="n">
+      <c r="E249" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="F249" s="6">
@@ -27759,7 +28052,7 @@
           <t>طعم ليه</t>
         </is>
       </c>
-      <c r="E250" s="21" t="n">
+      <c r="E250" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F250" s="6">
@@ -27797,7 +28090,7 @@
           <t>بابريكا</t>
         </is>
       </c>
-      <c r="E251" s="21" t="n">
+      <c r="E251" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F251" s="6">
@@ -27815,25 +28108,25 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="22" t="inlineStr">
+      <c r="A252" s="21" t="inlineStr">
         <is>
           <t>كفته الهنا</t>
         </is>
       </c>
-      <c r="B252" s="14" t="inlineStr">
+      <c r="B252" s="13" t="inlineStr">
         <is>
           <t>إجمالى الوصفة الرئيسية</t>
         </is>
       </c>
-      <c r="E252" s="23">
+      <c r="E252" s="22">
         <f>SUM(E229:E251)</f>
         <v/>
       </c>
-      <c r="G252" s="24">
+      <c r="G252" s="23">
         <f>SUM(G229:G251)</f>
         <v/>
       </c>
-      <c r="H252" s="22" t="inlineStr">
+      <c r="H252" s="21" t="inlineStr">
         <is>
           <t>سعر الكجم = قيمة الوصفة ÷ 394.39 كجم</t>
         </is>
@@ -27936,7 +28229,7 @@
       <c r="E4" s="6" t="n">
         <v>82.5378324326162</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <f>D4/H4</f>
         <v/>
       </c>
@@ -27944,7 +28237,7 @@
         <f>F4/E4-1</f>
         <v/>
       </c>
-      <c r="H4" s="25" t="n">
+      <c r="H4" s="24" t="n">
         <v>98.96003142968441</v>
       </c>
     </row>
@@ -27969,7 +28262,7 @@
       <c r="E5" s="6" t="n">
         <v>79.03417184076433</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <f>D5/H5</f>
         <v/>
       </c>
@@ -27977,7 +28270,7 @@
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="24" t="n">
         <v>78.5</v>
       </c>
     </row>
@@ -28002,7 +28295,7 @@
       <c r="E6" s="6" t="n">
         <v>76.22912748384007</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <f>D6/H6</f>
         <v/>
       </c>
@@ -28010,7 +28303,7 @@
         <f>F6/E6-1</f>
         <v/>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="24" t="n">
         <v>62.655</v>
       </c>
     </row>
@@ -28035,7 +28328,7 @@
       <c r="E7" s="6" t="n">
         <v>23.63285373361394</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <f>D7/H7</f>
         <v/>
       </c>
@@ -28043,7 +28336,7 @@
         <f>F7/E7-1</f>
         <v/>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="24" t="n">
         <v>394.39</v>
       </c>
     </row>
@@ -28068,7 +28361,7 @@
       <c r="E8" s="6" t="n">
         <v>24.53861676616276</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <f>D8/H8</f>
         <v/>
       </c>
@@ -28076,7 +28369,7 @@
         <f>F8/E8-1</f>
         <v/>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="24" t="n">
         <v>228.65888</v>
       </c>
     </row>
@@ -28101,7 +28394,7 @@
       <c r="E9" s="6" t="n">
         <v>31.10723840722496</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <f>D9/H9</f>
         <v/>
       </c>
@@ -28109,7 +28402,7 @@
         <f>F9/E9-1</f>
         <v/>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="24" t="n">
         <v>365.4</v>
       </c>
     </row>
@@ -28134,7 +28427,7 @@
       <c r="E10" s="6" t="n">
         <v>23.64191941388718</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <f>D10/H10</f>
         <v/>
       </c>
@@ -28142,7 +28435,7 @@
         <f>F10/E10-1</f>
         <v/>
       </c>
-      <c r="H10" s="25" t="n">
+      <c r="H10" s="24" t="n">
         <v>227.26</v>
       </c>
     </row>
@@ -28167,7 +28460,7 @@
       <c r="E11" s="6" t="n">
         <v>24.21680153921272</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <f>D11/H11</f>
         <v/>
       </c>
@@ -28175,7 +28468,7 @@
         <f>F11/E11-1</f>
         <v/>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="24" t="n">
         <v>430.09</v>
       </c>
     </row>
@@ -28200,7 +28493,7 @@
       <c r="E12" s="6" t="n">
         <v>23.63285373361394</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <f>D12/H12</f>
         <v/>
       </c>
@@ -28208,7 +28501,7 @@
         <f>F12/E12-1</f>
         <v/>
       </c>
-      <c r="H12" s="25" t="n">
+      <c r="H12" s="24" t="n">
         <v>394.39</v>
       </c>
     </row>
@@ -28395,7 +28688,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 3 كجم × سعر كجم سبتمبر + تعبئة 9.23 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 3 كجم × سعر كجم سبتمبر + تعبئة 9.23 ج.م</t>
         </is>
       </c>
     </row>
@@ -28425,7 +28718,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -28455,7 +28748,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 0.8 كجم × سعر كجم سبتمبر + تعبئة 6.27 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 0.8 كجم × سعر كجم سبتمبر + تعبئة 6.27 ج.م</t>
         </is>
       </c>
     </row>
@@ -28485,7 +28778,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 4.67 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 4.67 ج.م</t>
         </is>
       </c>
     </row>
@@ -28515,7 +28808,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته ابوهاشم»: 0.8 كجم × سعر كجم سبتمبر + تعبئة 5.35 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته ابوهاشم»: 0.8 كجم × سعر كجم سبتمبر + تعبئة 5.35 ج.م</t>
         </is>
       </c>
     </row>
@@ -28545,7 +28838,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته ابوهاشم»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 4.50 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته ابوهاشم»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 4.50 ج.م</t>
         </is>
       </c>
     </row>
@@ -28575,7 +28868,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر ابوهاشم»: 1.5 كجم × سعر كجم سبتمبر + تعبئة 6.07 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر ابوهاشم»: 1.5 كجم × سعر كجم سبتمبر + تعبئة 6.07 ج.م</t>
         </is>
       </c>
     </row>
@@ -28605,7 +28898,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر ابوهاشم»: 1.1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر ابوهاشم»: 1.1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -28635,7 +28928,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر ابوهاشم»: 0.8 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر ابوهاشم»: 0.8 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -28665,7 +28958,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر ابوهاشم»: 0.6 كجم × سعر كجم سبتمبر + تعبئة 5.99 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر ابوهاشم»: 0.6 كجم × سعر كجم سبتمبر + تعبئة 5.99 ج.م</t>
         </is>
       </c>
     </row>
@@ -28695,7 +28988,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر ابوهاشم»: 0.4 كجم × سعر كجم سبتمبر + تعبئة 4.99 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر ابوهاشم»: 0.4 كجم × سعر كجم سبتمبر + تعبئة 4.99 ج.م</t>
         </is>
       </c>
     </row>
@@ -28850,7 +29143,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -28955,7 +29248,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر ابوهاشم»: 1.2 كجم × سعر كجم سبتمبر + تعبئة 6.18 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر ابوهاشم»: 1.2 كجم × سعر كجم سبتمبر + تعبئة 6.18 ج.م</t>
         </is>
       </c>
     </row>
@@ -29010,7 +29303,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر ابوهاشم»: 1 كجم × سعر كجم سبتمبر + تعبئة 5.60 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر ابوهاشم»: 1 كجم × سعر كجم سبتمبر + تعبئة 5.60 ج.م</t>
         </is>
       </c>
     </row>
@@ -29065,7 +29358,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29095,7 +29388,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته ابوهاشم»: 5 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته ابوهاشم»: 5 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29125,7 +29418,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته ابوهاشم»: 1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته ابوهاشم»: 1 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29180,7 +29473,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 1.5 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 1.5 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29210,7 +29503,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق ابوهاشم»: 3 كجم × سعر كجم سبتمبر + تعبئة 9.23 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق ابوهاشم»: 3 كجم × سعر كجم سبتمبر + تعبئة 9.23 ج.م</t>
         </is>
       </c>
     </row>
@@ -29265,7 +29558,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق الهنا»: 0.7 كجم × سعر كجم سبتمبر + تعبئة 5.99 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق الهنا»: 0.7 كجم × سعر كجم سبتمبر + تعبئة 5.99 ج.م</t>
         </is>
       </c>
     </row>
@@ -29295,7 +29588,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق الهنا»: 0.3 كجم × سعر كجم سبتمبر + تعبئة 4.63 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق الهنا»: 0.3 كجم × سعر كجم سبتمبر + تعبئة 4.63 ج.م</t>
         </is>
       </c>
     </row>
@@ -29325,7 +29618,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته الهنا»: 0.8 كجم × سعر كجم سبتمبر + تعبئة 6.08 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته الهنا»: 0.8 كجم × سعر كجم سبتمبر + تعبئة 6.08 ج.م</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29648,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته الهنا»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 5.18 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته الهنا»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 5.18 ج.م</t>
         </is>
       </c>
     </row>
@@ -29385,7 +29678,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر الهنا»: 0.8 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر الهنا»: 0.8 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29708,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر الهنا»: 0.9 كجم × سعر كجم سبتمبر + تعبئة 6.63 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر الهنا»: 0.9 كجم × سعر كجم سبتمبر + تعبئة 6.63 ج.م</t>
         </is>
       </c>
     </row>
@@ -29445,7 +29738,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر الهنا»: 0.35 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر الهنا»: 0.35 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29475,7 +29768,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق الهنا»: 3 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق الهنا»: 3 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29505,7 +29798,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق الهنا»: 5 كجم × سعر كجم سبتمبر + تعبئة 16.06 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق الهنا»: 5 كجم × سعر كجم سبتمبر + تعبئة 16.06 ج.م</t>
         </is>
       </c>
     </row>
@@ -29618,7 +29911,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق الهنا»: 5 كجم × سعر كجم سبتمبر + تعبئة 16.06 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق الهنا»: 5 كجم × سعر كجم سبتمبر + تعبئة 16.06 ج.م</t>
         </is>
       </c>
     </row>
@@ -29648,7 +29941,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق الهنا»: 0.2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق الهنا»: 0.2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29678,7 +29971,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر الهنا»: 0.3 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر الهنا»: 0.3 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29708,7 +30001,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته الهنا»: 0.2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته الهنا»: 0.2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -29792,7 +30085,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر اسبشيال»: 1 كجم × سعر كجم سبتمبر + تعبئة 6.70 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر اسبشيال»: 1 كجم × سعر كجم سبتمبر + تعبئة 6.70 ج.م</t>
         </is>
       </c>
     </row>
@@ -29822,7 +30115,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «برجر اسبشيال»: 0.4 كجم × سعر كجم سبتمبر + تعبئة 5.50 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «برجر اسبشيال»: 0.4 كجم × سعر كجم سبتمبر + تعبئة 5.50 ج.م</t>
         </is>
       </c>
     </row>
@@ -29852,7 +30145,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته اسبشيال»: 0.9 كجم × سعر كجم سبتمبر + تعبئة 7.20 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته اسبشيال»: 0.9 كجم × سعر كجم سبتمبر + تعبئة 7.20 ج.م</t>
         </is>
       </c>
     </row>
@@ -29882,7 +30175,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته اسبشيال»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 5.50 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته اسبشيال»: 0.35 كجم × سعر كجم سبتمبر + تعبئة 5.50 ج.م</t>
         </is>
       </c>
     </row>
@@ -29912,7 +30205,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق اسبشيال»: 0.7 كجم × سعر كجم سبتمبر + تعبئة 7.20 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق اسبشيال»: 0.7 كجم × سعر كجم سبتمبر + تعبئة 7.20 ج.م</t>
         </is>
       </c>
     </row>
@@ -29942,7 +30235,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق اسبشيال»: 0.3 كجم × سعر كجم سبتمبر + تعبئة 5.20 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق اسبشيال»: 0.3 كجم × سعر كجم سبتمبر + تعبئة 5.20 ج.م</t>
         </is>
       </c>
     </row>
@@ -30059,7 +30352,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «سجق اسبشيال»: 5 كجم × سعر كجم سبتمبر + تعبئة 14.00 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «سجق اسبشيال»: 5 كجم × سعر كجم سبتمبر + تعبئة 14.00 ج.م</t>
         </is>
       </c>
     </row>
@@ -30816,7 +31109,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته ابوهاشم»: 2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة) | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته ابوهاشم»: 2 كجم × سعر كجم سبتمبر بدون تكلفة تعبئة (غير محددة بالوصفة)</t>
         </is>
       </c>
     </row>
@@ -30921,7 +31214,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>من وصفة «كفته الهنا»: 5 كجم × سعر كجم سبتمبر + تعبئة 14.26 ج.م | مؤقت: الوصفة تستخدم مفروم الفراخ بسعر أغسطس لحين حسم الفاتورة</t>
+          <t>من وصفة «كفته الهنا»: 5 كجم × سعر كجم سبتمبر + تعبئة 14.26 ج.م</t>
         </is>
       </c>
     </row>
@@ -31090,23 +31383,23 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t>إجمالى قيمة مخزون المنتج التام آخر سبتمبر (الأصناف المُسعّرة)</t>
         </is>
       </c>
-      <c r="F107" s="13">
+      <c r="F107" s="12">
         <f>SUM(F4:F105)</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="12" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>إجمالى قيمة المخزون الكلى آخر سبتمبر (خامات + منتج تام)</t>
         </is>
       </c>
-      <c r="F109" s="13">
+      <c r="F109" s="12">
         <f>F107+'احتساب متوسط سبتمبر'!L171</f>
         <v/>
       </c>
@@ -31125,10 +31418,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -31136,7 +31429,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>صنفا الفراخ المفرومة — بيانات شراء متعارضة (السعر بملف سبتمبر تُرك كما هو)</t>
+          <t>صنفا الفراخ المفرومة — تصحيح الفاتورة 1111115217 (معتمد بتأكيد الإدارة)</t>
         </is>
       </c>
     </row>
@@ -31184,15 +31477,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>متوسط سبتمبر — بعكس سعرَى الفاتورة (C=30، A=57)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>متوسط سبتمبر — بعكس سعرَى الفاتورة (C=30، A=57) — المعتمد</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>31.8123</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>57.9003</v>
       </c>
     </row>
@@ -31212,7 +31505,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>السعر الموجود بملف سبتمبر (تُرك)</t>
+          <t>السعر الذى كان بملف جرد سبتمبر</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -31223,31 +31516,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>السعر المُدخل بملف سبتمبر الآن</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>31.8123</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>57.9003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كمية جرد 30/9</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B10" s="5" t="n">
         <v>860</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>370</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>فاتورة 1111115217 (09/09): «مفروم فراخ C» 1,500 كجم بسعر 57 بينما نطاق الرتبة C 30–35، وفى نفس الفاتورة «مفروم فراخ A» بسعر 30 بينما نطاق A 55–60 — السعران يبدوان معكوسين</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="27" t="n"/>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>فاتورة 1111115217 (09/09) سجّلت «مفروم فراخ C» بسعر 57 و«مفروم فراخ A» بسعر 30 (خارج نطاق كل رتبة)؛ أكدت الإدارة أن السعرين معكوسان فاحتُسبت C = 30 و A = 57</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31259,7 +31565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -31306,22 +31612,22 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>إجمالى أسطر مشتريات سبتمبر = الإجمالى المطبوع بالتقرير</t>
+          <t>إجمالى أسطر مشتريات سبتمبر كما سُجّلت = الإجمالى المطبوع بالتقرير</t>
         </is>
       </c>
       <c r="B4" s="5">
-        <f>'مشتريات سبتمبر التفصيلية'!H94</f>
+        <f>'مشتريات سبتمبر التفصيلية'!M94</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>'مشتريات سبتمبر التفصيلية'!H95</f>
+        <f>'مشتريات سبتمبر التفصيلية'!M95</f>
         <v/>
       </c>
       <c r="D4" s="5">
         <f>B4-C4</f>
         <v/>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="19">
         <f>IF(ABS(D4)&lt;=0.005,"✔ مطابق","✘ فرق")</f>
         <v/>
       </c>
@@ -31329,22 +31635,21 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>المشتريات المحمّلة على الأصناف + المجمّع + المستبعدة = إجمالى المشتريات</t>
+          <t>أثر تصحيح الفاتورة 1111115217 = Σ الكمية × (السعر المصحّح − المسجّل)</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'احتساب متوسط سبتمبر'!F171+'احتساب متوسط سبتمبر'!F174+'مشتريات سبتمبر التفصيلية'!H96</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>'مشتريات سبتمبر التفصيلية'!H94</f>
-        <v/>
+        <f>'مشتريات سبتمبر التفصيلية'!H97</f>
+        <v/>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-28350</v>
       </c>
       <c r="D5" s="5">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="19">
         <f>IF(ABS(D5)&lt;=0.005,"✔ مطابق","✘ فرق")</f>
         <v/>
       </c>
@@ -31352,22 +31657,22 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>قيمة أول المدة بورقة الاحتساب = قيمة أصناف جرد 31/8 المنقولة لسبتمبر</t>
+          <t>المشتريات المحمّلة على الأصناف + المجمّع + المستبعدة = إجمالى المشتريات</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>'احتساب متوسط سبتمبر'!D171</f>
+        <f>'احتساب متوسط سبتمبر'!F171+'احتساب متوسط سبتمبر'!F174+'مشتريات سبتمبر التفصيلية'!H96</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>N('رصيد أول المدة (31-8)'!F5)+N('رصيد أول المدة (31-8)'!F6)+N('رصيد أول المدة (31-8)'!F7)+N('رصيد أول المدة (31-8)'!F8)+N('رصيد أول المدة (31-8)'!F9)+N('رصيد أول المدة (31-8)'!F10)+N('رصيد أول المدة (31-8)'!F11)+N('رصيد أول المدة (31-8)'!F12)+N('رصيد أول المدة (31-8)'!F13)+N('رصيد أول المدة (31-8)'!F14)+N('رصيد أول المدة (31-8)'!F15)+N('رصيد أول المدة (31-8)'!F16)+N('رصيد أول المدة (31-8)'!F17)+N('رصيد أول المدة (31-8)'!F18)+N('رصيد أول المدة (31-8)'!F19)+N('رصيد أول المدة (31-8)'!F20)+N('رصيد أول المدة (31-8)'!F21)+N('رصيد أول المدة (31-8)'!F22)+N('رصيد أول المدة (31-8)'!F23)+N('رصيد أول المدة (31-8)'!F24)+N('رصيد أول المدة (31-8)'!F25)+N('رصيد أول المدة (31-8)'!F26)+N('رصيد أول المدة (31-8)'!F27)+N('رصيد أول المدة (31-8)'!F28)+N('رصيد أول المدة (31-8)'!F29)+N('رصيد أول المدة (31-8)'!F30)+N('رصيد أول المدة (31-8)'!F31)+N('رصيد أول المدة (31-8)'!F32)+N('رصيد أول المدة (31-8)'!F33)+N('رصيد أول المدة (31-8)'!F34)+N('رصيد أول المدة (31-8)'!F35)+N('رصيد أول المدة (31-8)'!F36)+N('رصيد أول المدة (31-8)'!F37)+N('رصيد أول المدة (31-8)'!F38)+N('رصيد أول المدة (31-8)'!F39)+N('رصيد أول المدة (31-8)'!F40)+N('رصيد أول المدة (31-8)'!F41)+N('رصيد أول المدة (31-8)'!F42)+N('رصيد أول المدة (31-8)'!F43)+N('رصيد أول المدة (31-8)'!F44)+N('رصيد أول المدة (31-8)'!F45)+N('رصيد أول المدة (31-8)'!F46)+N('رصيد أول المدة (31-8)'!F47)+N('رصيد أول المدة (31-8)'!F48)+N('رصيد أول المدة (31-8)'!F49)+N('رصيد أول المدة (31-8)'!F50)+N('رصيد أول المدة (31-8)'!F51)+N('رصيد أول المدة (31-8)'!F52)+N('رصيد أول المدة (31-8)'!F53)+N('رصيد أول المدة (31-8)'!F54)+N('رصيد أول المدة (31-8)'!F55)+N('رصيد أول المدة (31-8)'!F56)+N('رصيد أول المدة (31-8)'!F57)+N('رصيد أول المدة (31-8)'!F58)+N('رصيد أول المدة (31-8)'!F59)+N('رصيد أول المدة (31-8)'!F60)+N('رصيد أول المدة (31-8)'!F61)+N('رصيد أول المدة (31-8)'!F62)+N('رصيد أول المدة (31-8)'!F63)+N('رصيد أول المدة (31-8)'!F64)+N('رصيد أول المدة (31-8)'!F65)+N('رصيد أول المدة (31-8)'!F66)+N('رصيد أول المدة (31-8)'!F67)+N('رصيد أول المدة (31-8)'!F68)+N('رصيد أول المدة (31-8)'!F69)+N('رصيد أول المدة (31-8)'!F70)+N('رصيد أول المدة (31-8)'!F71)+N('رصيد أول المدة (31-8)'!F72)+N('رصيد أول المدة (31-8)'!F73)+N('رصيد أول المدة (31-8)'!F74)+N('رصيد أول المدة (31-8)'!F75)+N('رصيد أول المدة (31-8)'!F76)+N('رصيد أول المدة (31-8)'!F77)+N('رصيد أول المدة (31-8)'!F78)+N('رصيد أول المدة (31-8)'!F79)+N('رصيد أول المدة (31-8)'!F80)+N('رصيد أول المدة (31-8)'!F81)+N('رصيد أول المدة (31-8)'!F82)+N('رصيد أول المدة (31-8)'!F83)+N('رصيد أول المدة (31-8)'!F84)+N('رصيد أول المدة (31-8)'!F85)+N('رصيد أول المدة (31-8)'!F86)+N('رصيد أول المدة (31-8)'!F87)+N('رصيد أول المدة (31-8)'!F88)+N('رصيد أول المدة (31-8)'!F89)+N('رصيد أول المدة (31-8)'!F90)+N('رصيد أول المدة (31-8)'!F91)+N('رصيد أول المدة (31-8)'!F92)+N('رصيد أول المدة (31-8)'!F93)+N('رصيد أول المدة (31-8)'!F94)+N('رصيد أول المدة (31-8)'!F95)+N('رصيد أول المدة (31-8)'!F96)+N('رصيد أول المدة (31-8)'!F97)+N('رصيد أول المدة (31-8)'!F98)+N('رصيد أول المدة (31-8)'!F99)+N('رصيد أول المدة (31-8)'!F100)+N('رصيد أول المدة (31-8)'!F101)+N('رصيد أول المدة (31-8)'!F102)+N('رصيد أول المدة (31-8)'!F103)+N('رصيد أول المدة (31-8)'!F104)+N('رصيد أول المدة (31-8)'!F105)+N('رصيد أول المدة (31-8)'!F106)+N('رصيد أول المدة (31-8)'!F107)+N('رصيد أول المدة (31-8)'!F108)+N('رصيد أول المدة (31-8)'!F109)+N('رصيد أول المدة (31-8)'!F110)+N('رصيد أول المدة (31-8)'!F111)+N('رصيد أول المدة (31-8)'!F112)+N('رصيد أول المدة (31-8)'!F113)+N('رصيد أول المدة (31-8)'!F143)+N('رصيد أول المدة (31-8)'!F114)+N('رصيد أول المدة (31-8)'!F115)+N('رصيد أول المدة (31-8)'!F116)+N('رصيد أول المدة (31-8)'!F117)+N('رصيد أول المدة (31-8)'!F118)+N('رصيد أول المدة (31-8)'!F119)+N('رصيد أول المدة (31-8)'!F120)+N('رصيد أول المدة (31-8)'!F121)+N('رصيد أول المدة (31-8)'!F123)+N('رصيد أول المدة (31-8)'!F124)+N('رصيد أول المدة (31-8)'!F125)+N('رصيد أول المدة (31-8)'!F126)+N('رصيد أول المدة (31-8)'!F127)+N('رصيد أول المدة (31-8)'!F128)+N('رصيد أول المدة (31-8)'!F129)+N('رصيد أول المدة (31-8)'!F130)+N('رصيد أول المدة (31-8)'!F131)+N('رصيد أول المدة (31-8)'!F132)+N('رصيد أول المدة (31-8)'!F133)+N('رصيد أول المدة (31-8)'!F134)+N('رصيد أول المدة (31-8)'!F135)+N('رصيد أول المدة (31-8)'!F136)+N('رصيد أول المدة (31-8)'!F137)+N('رصيد أول المدة (31-8)'!F138)+N('رصيد أول المدة (31-8)'!F140)+N('رصيد أول المدة (31-8)'!F139)+N('رصيد أول المدة (31-8)'!F146)+N('رصيد أول المدة (31-8)'!F151)+N('رصيد أول المدة (31-8)'!F147)+N('رصيد أول المدة (31-8)'!F148)+N('رصيد أول المدة (31-8)'!F149)+N('رصيد أول المدة (31-8)'!F150)+N('رصيد أول المدة (31-8)'!F141)+N('رصيد أول المدة (31-8)'!F142)+N('رصيد أول المدة (31-8)'!F144)+N('رصيد أول المدة (31-8)'!F152)+N('رصيد أول المدة (31-8)'!F145)</f>
+        <f>'مشتريات سبتمبر التفصيلية'!H94</f>
         <v/>
       </c>
       <c r="D6" s="5">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <f>IF(ABS(D6)&lt;=0.005,"✔ مطابق","✘ فرق")</f>
         <v/>
       </c>
@@ -31375,58 +31680,60 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>قيمة مخزون الخامات 30/9 = Σ (كمية جرد 30/9 × السعر المُدخل بالملف)</t>
+          <t>قيمة أول المدة بورقة الاحتساب = قيمة أصناف جرد 31/8 المنقولة لسبتمبر</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <f>'احتساب متوسط سبتمبر'!L171</f>
+        <f>'احتساب متوسط سبتمبر'!D171</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>SUMPRODUCT('احتساب متوسط سبتمبر'!K5:K169,'احتساب متوسط سبتمبر'!J5:J169)</f>
+        <f>N('رصيد أول المدة (31-8)'!F5)+N('رصيد أول المدة (31-8)'!F6)+N('رصيد أول المدة (31-8)'!F7)+N('رصيد أول المدة (31-8)'!F8)+N('رصيد أول المدة (31-8)'!F9)+N('رصيد أول المدة (31-8)'!F10)+N('رصيد أول المدة (31-8)'!F11)+N('رصيد أول المدة (31-8)'!F12)+N('رصيد أول المدة (31-8)'!F13)+N('رصيد أول المدة (31-8)'!F14)+N('رصيد أول المدة (31-8)'!F15)+N('رصيد أول المدة (31-8)'!F16)+N('رصيد أول المدة (31-8)'!F17)+N('رصيد أول المدة (31-8)'!F18)+N('رصيد أول المدة (31-8)'!F19)+N('رصيد أول المدة (31-8)'!F20)+N('رصيد أول المدة (31-8)'!F21)+N('رصيد أول المدة (31-8)'!F22)+N('رصيد أول المدة (31-8)'!F23)+N('رصيد أول المدة (31-8)'!F24)+N('رصيد أول المدة (31-8)'!F25)+N('رصيد أول المدة (31-8)'!F26)+N('رصيد أول المدة (31-8)'!F27)+N('رصيد أول المدة (31-8)'!F28)+N('رصيد أول المدة (31-8)'!F29)+N('رصيد أول المدة (31-8)'!F30)+N('رصيد أول المدة (31-8)'!F31)+N('رصيد أول المدة (31-8)'!F32)+N('رصيد أول المدة (31-8)'!F33)+N('رصيد أول المدة (31-8)'!F34)+N('رصيد أول المدة (31-8)'!F35)+N('رصيد أول المدة (31-8)'!F36)+N('رصيد أول المدة (31-8)'!F37)+N('رصيد أول المدة (31-8)'!F38)+N('رصيد أول المدة (31-8)'!F39)+N('رصيد أول المدة (31-8)'!F40)+N('رصيد أول المدة (31-8)'!F41)+N('رصيد أول المدة (31-8)'!F42)+N('رصيد أول المدة (31-8)'!F43)+N('رصيد أول المدة (31-8)'!F44)+N('رصيد أول المدة (31-8)'!F45)+N('رصيد أول المدة (31-8)'!F46)+N('رصيد أول المدة (31-8)'!F47)+N('رصيد أول المدة (31-8)'!F48)+N('رصيد أول المدة (31-8)'!F49)+N('رصيد أول المدة (31-8)'!F50)+N('رصيد أول المدة (31-8)'!F51)+N('رصيد أول المدة (31-8)'!F52)+N('رصيد أول المدة (31-8)'!F53)+N('رصيد أول المدة (31-8)'!F54)+N('رصيد أول المدة (31-8)'!F55)+N('رصيد أول المدة (31-8)'!F56)+N('رصيد أول المدة (31-8)'!F57)+N('رصيد أول المدة (31-8)'!F58)+N('رصيد أول المدة (31-8)'!F59)+N('رصيد أول المدة (31-8)'!F60)+N('رصيد أول المدة (31-8)'!F61)+N('رصيد أول المدة (31-8)'!F62)+N('رصيد أول المدة (31-8)'!F63)+N('رصيد أول المدة (31-8)'!F64)+N('رصيد أول المدة (31-8)'!F65)+N('رصيد أول المدة (31-8)'!F66)+N('رصيد أول المدة (31-8)'!F67)+N('رصيد أول المدة (31-8)'!F68)+N('رصيد أول المدة (31-8)'!F69)+N('رصيد أول المدة (31-8)'!F70)+N('رصيد أول المدة (31-8)'!F71)+N('رصيد أول المدة (31-8)'!F72)+N('رصيد أول المدة (31-8)'!F73)+N('رصيد أول المدة (31-8)'!F74)+N('رصيد أول المدة (31-8)'!F75)+N('رصيد أول المدة (31-8)'!F76)+N('رصيد أول المدة (31-8)'!F77)+N('رصيد أول المدة (31-8)'!F78)+N('رصيد أول المدة (31-8)'!F79)+N('رصيد أول المدة (31-8)'!F80)+N('رصيد أول المدة (31-8)'!F81)+N('رصيد أول المدة (31-8)'!F82)+N('رصيد أول المدة (31-8)'!F83)+N('رصيد أول المدة (31-8)'!F84)+N('رصيد أول المدة (31-8)'!F85)+N('رصيد أول المدة (31-8)'!F86)+N('رصيد أول المدة (31-8)'!F87)+N('رصيد أول المدة (31-8)'!F88)+N('رصيد أول المدة (31-8)'!F89)+N('رصيد أول المدة (31-8)'!F90)+N('رصيد أول المدة (31-8)'!F91)+N('رصيد أول المدة (31-8)'!F92)+N('رصيد أول المدة (31-8)'!F93)+N('رصيد أول المدة (31-8)'!F94)+N('رصيد أول المدة (31-8)'!F95)+N('رصيد أول المدة (31-8)'!F96)+N('رصيد أول المدة (31-8)'!F97)+N('رصيد أول المدة (31-8)'!F98)+N('رصيد أول المدة (31-8)'!F99)+N('رصيد أول المدة (31-8)'!F100)+N('رصيد أول المدة (31-8)'!F101)+N('رصيد أول المدة (31-8)'!F102)+N('رصيد أول المدة (31-8)'!F103)+N('رصيد أول المدة (31-8)'!F104)+N('رصيد أول المدة (31-8)'!F105)+N('رصيد أول المدة (31-8)'!F106)+N('رصيد أول المدة (31-8)'!F107)+N('رصيد أول المدة (31-8)'!F108)+N('رصيد أول المدة (31-8)'!F109)+N('رصيد أول المدة (31-8)'!F110)+N('رصيد أول المدة (31-8)'!F111)+N('رصيد أول المدة (31-8)'!F112)+N('رصيد أول المدة (31-8)'!F113)+N('رصيد أول المدة (31-8)'!F143)+N('رصيد أول المدة (31-8)'!F114)+N('رصيد أول المدة (31-8)'!F115)+N('رصيد أول المدة (31-8)'!F116)+N('رصيد أول المدة (31-8)'!F117)+N('رصيد أول المدة (31-8)'!F118)+N('رصيد أول المدة (31-8)'!F119)+N('رصيد أول المدة (31-8)'!F120)+N('رصيد أول المدة (31-8)'!F121)+N('رصيد أول المدة (31-8)'!F123)+N('رصيد أول المدة (31-8)'!F124)+N('رصيد أول المدة (31-8)'!F125)+N('رصيد أول المدة (31-8)'!F126)+N('رصيد أول المدة (31-8)'!F127)+N('رصيد أول المدة (31-8)'!F128)+N('رصيد أول المدة (31-8)'!F129)+N('رصيد أول المدة (31-8)'!F130)+N('رصيد أول المدة (31-8)'!F131)+N('رصيد أول المدة (31-8)'!F132)+N('رصيد أول المدة (31-8)'!F133)+N('رصيد أول المدة (31-8)'!F134)+N('رصيد أول المدة (31-8)'!F135)+N('رصيد أول المدة (31-8)'!F136)+N('رصيد أول المدة (31-8)'!F137)+N('رصيد أول المدة (31-8)'!F138)+N('رصيد أول المدة (31-8)'!F140)+N('رصيد أول المدة (31-8)'!F139)+N('رصيد أول المدة (31-8)'!F146)+N('رصيد أول المدة (31-8)'!F151)+N('رصيد أول المدة (31-8)'!F147)+N('رصيد أول المدة (31-8)'!F148)+N('رصيد أول المدة (31-8)'!F149)+N('رصيد أول المدة (31-8)'!F150)+N('رصيد أول المدة (31-8)'!F141)+N('رصيد أول المدة (31-8)'!F142)+N('رصيد أول المدة (31-8)'!F144)+N('رصيد أول المدة (31-8)'!F152)+N('رصيد أول المدة (31-8)'!F145)</f>
         <v/>
       </c>
       <c r="D7" s="5">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="20">
-        <f>IF(ABS(D7)&lt;=0.01,"✔ مطابق","✘ فرق")</f>
+      <c r="E7" s="19">
+        <f>IF(ABS(D7)&lt;=0.005,"✔ مطابق","✘ فرق")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>أسعار ملف «تسعير جرد اخر شهر ٩» = الاحتساب المستقل (عدد الأصناف)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>165</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>165</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>✔ مطابق</t>
-        </is>
+          <t>قيمة مخزون الخامات 30/9 = Σ (كمية جرد 30/9 × السعر المُدخل بالملف)</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>'احتساب متوسط سبتمبر'!L171</f>
+        <v/>
+      </c>
+      <c r="C8" s="5">
+        <f>SUMPRODUCT('احتساب متوسط سبتمبر'!K5:K169,'احتساب متوسط سبتمبر'!J5:J169)</f>
+        <v/>
+      </c>
+      <c r="D8" s="5">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
+        <f>IF(ABS(D8)&lt;=0.01,"✔ مطابق","✘ فرق")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>قيمة مخزون الخامات بملف سبتمبر بعد إعادة الاحتساب (Σ عمود القيمة)</t>
+          <t>أسعار ملف «تسعير جرد اخر شهر ٩» = الاحتساب المستقل (عدد الأصناف)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>2202045.11</v>
+        <v>165</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2202045.11</v>
+        <v>165</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>0</v>
@@ -31440,17 +31747,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>قيمة جرد 31/8 المعدَّل × متوسط أغسطس = إجمالى ملف «-2» + أثر فروق الكميات بينهما (-19,014.85، أغلبه «زيت سيارات» 2 بالجرد مقابل 16 بملف «-2»)</t>
+          <t>قيمة مخزون الخامات بملف سبتمبر بعد إعادة الاحتساب (Σ عمود القيمة)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>2642846.25</v>
+        <v>2202826.8</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2642846.24</v>
+        <v>2202826.8</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.009999999776482582</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -31461,19 +31768,40 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>قيمة جرد 31/8 المعدَّل × متوسط أغسطس = إجمالى ملف «-2» + أثر فروق الكميات بينهما (-19,014.85، أغلبه «زيت سيارات» 2 بالجرد مقابل 16 بملف «-2»)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2642846.25</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2642846.24</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.009999999776482582</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>✔ مطابق</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>أصناف جرد 31/8 ذات قيمة غير موجودة بجرد سبتمبر (قيمة)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>✔ مطابق</t>
         </is>
@@ -31493,7 +31821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -31509,7 +31837,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>نطاق العمل</t>
         </is>
@@ -31519,10 +31847,10 @@
           <t>متوسط التكلفة المرجّح (WAC) للخامات فقط — لم تُستخدم FIFO / LIFO / التكلفة المعيارية.</t>
         </is>
       </c>
-      <c r="C3" s="27" t="n"/>
+      <c r="C3" s="26" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>المعادلة</t>
         </is>
@@ -31532,10 +31860,10 @@
           <t>متوسط سبتمبر = (كمية جرد 31/8 × متوسط أغسطس + قيمة مشتريات سبتمبر) ÷ (كمية جرد 31/8 + كمية مشتريات سبتمبر). يُحتسب بالدقة الكاملة ويُقرَّب السعر المُدخل لأربعة أرقام عشرية.</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n"/>
+      <c r="C4" s="26" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>رصيد أول المدة</t>
         </is>
@@ -31545,23 +31873,23 @@
           <t>الجرد الفعلى المعدَّل «جر د شهر 8.xlsx» (مجموع المواقع الخمسة) × متوسط أغسطس المُعاد احتسابه من مصادره؛ طوبق السعر مع ملف «تسعير جرد اخر شهر ٨ -2» لكل صنف مشترك (لا فرق).</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n"/>
+      <c r="C5" s="26" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>المشتريات</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>تقرير المشتريات 01/09–30/09/2026: 89 سطرًا، الإجمالى مطابق للمطبوع. قيمة الشراء = «الإجمالى» بالفاتورة (7 أسطر بها فرق تقريب بين الكمية × السعر والإجمالى). المحمَّل على الأصناف 2,197,994.05 ج.م.</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n"/>
+          <t>تقرير المشتريات 01/09–30/09/2026: 89 سطرًا، الإجمالى مطابق للمطبوع. قيمة الشراء = «الإجمالى» بالفاتورة (7 أسطر بها فرق تقريب بين الكمية × السعر والإجمالى)، بعد تصحيح سطرَى الفاتورة 1111115217 (أثر -28,350.00 ج.م). المحمَّل على الأصناف 2,169,644.05 ج.م.</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>ربط الأكواد</t>
         </is>
@@ -31571,23 +31899,23 @@
           <t>الكود المستخدم فى يوليو/أغسطس يُربط بنفس الصنف؛ الأكواد الجديدة رُبطت بالاسم ونطاق السعر بدرجة ثقة مُسجّلة. مجمّع اللحوم الهندى متوسط واحد للبنود الأربعة.</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n"/>
+      <c r="C7" s="26" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>أصناف معلّقة</t>
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>تصحيح فاتورة</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>صنفا الفراخ المفرومة (شعبي/فاخر) تُرك سعرهما بالملف كما هو لتعارض فاتورة 1111115217؛ ثلاث قراءات بديلة بورقة «الفراخ المفرومة (معلّق)». الوصفات تستخدم لهما سعر أغسطس مؤقتًا.</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n"/>
+          <t>فاتورة 1111115217 (09/09) سجّلت «مفروم فراخ C» بسعر 57 و«مفروم فراخ A» بسعر 30 (خارج نطاق كل رتبة)؛ أكدت الإدارة أن السعرين معكوسان فاحتُسبت C = 30 و A = 57. صنفا الفراخ المفرومة (شعبي/فاخر) سُعّرا بالمتوسط بعد التصحيح، والوصفات تستخدم هذا السعر؛ القراءات البديلة للإفصاح بورقة «الفراخ المفرومة (التصحيح)».</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n"/>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>أصناف بلا مشتريات</t>
         </is>
@@ -31597,23 +31925,23 @@
           <t>يبقى سعر أغسطس كما هو. رصيد بلا سعر يُستبعد من البسط والمقام.</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n"/>
+      <c r="C9" s="26" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>ملف سبتمبر</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>«تسعير جرد اخر شهر ٩ سنة ٢٠٢٦.xlsx» نسخة من «جرد شهر 9.xlsx» تغيّرت فيها خانات السعر فقط (عمود H للخامات و L للمنتج التام)؛ تحقق آلى من عدم تغيّر أى خانة أخرى. أُضيفت تعليقات على الأصناف المعلّقة أو بلا سعر.</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="n"/>
+          <t>«تسعير جرد اخر شهر ٩ سنة ٢٠٢٦.xlsx» نسخة من «جرد شهر 9.xlsx» تغيّرت فيها خانات السعر فقط (عمود H للخامات و L للمنتج التام)، وأُضيفت =K×L بعمود M الفارغ لصفوف المنتج التام المُسعّرة؛ تحقق آلى من عدم تغيّر أى خانة أخرى. الأصناف بلا سعر تُركت كما هى.</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n"/>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>المنتج التام</t>
         </is>
@@ -31623,7 +31951,7 @@
           <t>الوزن × سعر كجم الوصفة بأسعار سبتمبر + تكلفة التعبئة؛ الأصناف خارج الوصفات بآخر سعر متاح.</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n"/>
+      <c r="C11" s="26" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -31645,68 +31973,68 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>سعر معلّق</t>
+          <t>تصحيح سعر فاتورة</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>مفروم فراخ شعبي</t>
+          <t>سطر 24 كود 372 «مفروم فراخ C» ← مفروم فراخ شعبي</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>فاتورة 1111115217 (09/09): «مفروم فراخ C» 1,500 كجم بسعر 57 بينما نطاق الرتبة C 30–35، وفى نفس الفاتورة «مفروم فراخ A» بسعر 30 بينما نطاق A 55–60 — السعران يبدوان معكوسين — كما سُجّلت بالتقرير: 35.6294، باستبعاد الفاتورة 1111115217: 32.1107، بعكس سعرَى الفاتورة (C=30، A=57): 31.8123</t>
+          <t>المسجّل 57 × 1,500 = 85,500.00؛ المعتمد 30 × 1,500 = 45,000.00 (تأكيد الإدارة: السعران معكوسان)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>سعر معلّق</t>
+          <t>تصحيح سعر فاتورة</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>مفروم فراخ فاخر</t>
+          <t>سطر 25 كود 370 «مفروم فراخ A» ← مفروم فراخ فاخر</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>فاتورة 1111115217 (09/09): «مفروم فراخ A» 450 كجم بسعر 30 بينما نطاق الرتبة A 55–60، وفى نفس الفاتورة «مفروم فراخ C» بسعر 57 — السعران يبدوان معكوسين — كما سُجّلت بالتقرير: 50.3771، باستبعاد الفاتورة 1111115217: 58.2481، بعكس سعرَى الفاتورة (C=30، A=57): 57.9003</t>
+          <t>المسجّل 30 × 450 = 13,500.00؛ المعتمد 57 × 450 = 25,650.00 (تأكيد الإدارة: السعران معكوسان)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>ربط بثقة متوسطة</t>
+          <t>أثر التصحيح</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>كود 14 «تشكيله هندى امامى» ← @مجمع اللحوم الهندى</t>
+          <t>مفروم فراخ شعبي</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>نفس ربط الكود فى يوليو: لحوم هندى مجمَّعة: بنود (كتف/رقبه/سن/أرباع) بسعر يونيه موحَّد 253</t>
+          <t>السعر بالملف 30 ← 31.8123؛ القراءات: كما سُجّلت بالتقرير: 35.6294، باستبعاد الفاتورة 1111115217: 32.1107، بعكس سعرَى الفاتورة (C=30، A=57) — المعتمد: 31.8123</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>ربط بثقة متوسطة</t>
+          <t>أثر التصحيح</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>كود 40 «علب شفاف» ← علب بلاستيك شفاف</t>
+          <t>مفروم فراخ فاخر</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>نفس ربط الكود فى يوليو: تطابق اسمى؛ رصيد أول المدة كان بلا سعر ⇒ السعر = سعر الشراء</t>
+          <t>السعر بالملف 60 ← 57.9003؛ القراءات: كما سُجّلت بالتقرير: 50.3771، باستبعاد الفاتورة 1111115217: 58.2481، بعكس سعرَى الفاتورة (C=30، A=57) — المعتمد: 57.9003</t>
         </is>
       </c>
     </row>
@@ -31718,12 +32046,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>كود 409 «طبق شفاف كيلو» ← طبق مسطح 1 ك شفاف</t>
+          <t>كود 14 «تشكيله هندى امامى» ← @مجمع اللحوم الهندى</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>طبق شفاف كيلو = البند الشفاف الوحيد مقاس 1 ك بالجرد؛ بلا سعر سابق — يُراجَع</t>
+          <t>نفس ربط الكود فى يوليو: لحوم هندى مجمَّعة: بنود (كتف/رقبه/سن/أرباع) بسعر يونيه موحَّد 253</t>
         </is>
       </c>
     </row>
@@ -31735,12 +32063,12 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>كود 51 «صويا مصرى» ← صويا لحمه</t>
+          <t>كود 40 «علب شفاف» ← علب بلاستيك شفاف</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>نفس ربط الكود فى يوليو: الصويا العامة تُحمَّل على «صويا لحمه» (سعر 32–40 ≈ 39.44) — نفس افتراض ملف يونيه</t>
+          <t>نفس ربط الكود فى يوليو: تطابق اسمى؛ رصيد أول المدة كان بلا سعر ⇒ السعر = سعر الشراء</t>
         </is>
       </c>
     </row>
@@ -31752,148 +32080,148 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>كود 344 «فلفل حامى» ← فلفل رومي حامي</t>
+          <t>كود 409 «طبق شفاف كيلو» ← طبق مسطح 1 ك شفاف</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>فلفل حامى = عائلة الفلفل الحار الوحيدة بالجرد (نفس معالجة «فلفل احمر» كود 187)</t>
+          <t>طبق شفاف كيلو = البند الشفاف الوحيد مقاس 1 ك بالجرد؛ بلا سعر سابق — يُراجَع</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>شراء بلا مقابل</t>
+          <t>ربط بثقة متوسطة</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>كود 453 «ببريكا مدخنه» — 5,600.00 ج.م</t>
+          <t>كود 51 «صويا مصرى» ← صويا لحمه</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>بابريكا مدخنة صنف مختلف عن «بابريكا» العادية ولا يوجد له بند بالجرد — لم تُحمَّل على أى صنف</t>
+          <t>نفس ربط الكود فى يوليو: الصويا العامة تُحمَّل على «صويا لحمه» (سعر 32–40 ≈ 39.44) — نفس افتراض ملف يونيه</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>سعر شاذ (دخل كما سُجّل)</t>
+          <t>ربط بثقة متوسطة</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>سطر 58 كود 87 «جلتومات الصوديوم»</t>
+          <t>كود 344 «فلفل حامى» ← فلفل رومي حامي</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>نفس ربط الكود فى أغسطس: جلوتامات الصوديوم = «جلتومات/مونوصوديم» بالوصفات؛ سعر 88 مقابل 104.00 ليوليو | ⚠ جلتومات 25 كجم بسعر 132 مقابل 80 لسطر الشراء الآخر</t>
+          <t>فلفل حامى = عائلة الفلفل الحار الوحيدة بالجرد (نفس معالجة «فلفل احمر» كود 187)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>ربط بثقة متوسطة</t>
+          <t>شراء بلا مقابل</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>كود 154 «فلفل اخضر عام عام» ← فلفل بارد</t>
+          <t>كود 453 «ببريكا مدخنه» — 5,600.00 ج.م</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>نفس ربط الكود فى يوليو: الفلفل الأخضر غير الحار = «البارد»؛ سعر 12–14 ≈ 14.92 ليونيه</t>
+          <t>بابريكا مدخنة صنف مختلف عن «بابريكا» العادية ولا يوجد له بند بالجرد — لم تُحمَّل على أى صنف</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>ربط بثقة متوسطة</t>
+          <t>سعر شاذ (دخل كما سُجّل)</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>كود 371 «مفروم فراخ B» ← مفروم فراخ شعبي</t>
+          <t>سطر 58 كود 87 «جلتومات الصوديوم»</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>الرتبة B غير موجودة بالجرد؛ سعرها 34 داخل نطاق الرتبة C (30–35) فحُمّلت على «شعبي» — يُراجَع</t>
+          <t>نفس ربط الكود فى أغسطس: جلوتامات الصوديوم = «جلتومات/مونوصوديم» بالوصفات؛ سعر 88 مقابل 104.00 ليوليو | ⚠ جلتومات 25 كجم بسعر 132 مقابل 80 لسطر الشراء الآخر</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>سعر شاذ (دخل كما سُجّل)</t>
+          <t>ربط بثقة متوسطة</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>سطر 76 كود 190 «صميد»</t>
+          <t>كود 154 «فلفل اخضر عام عام» ← فلفل بارد</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>نفس ربط الكود فى يوليو: تطابق اسمى تام | ⚠ صميد 50 كجم بسعر 26.40 مقابل 16.25–17.00 لباقى الأسطر</t>
+          <t>نفس ربط الكود فى يوليو: الفلفل الأخضر غير الحار = «البارد»؛ سعر 12–14 ≈ 14.92 ليونيه</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>شراء بلا مقابل</t>
+          <t>ربط بثقة متوسطة</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>كود 442 «اكياس تغليف مقطعات 5ك» — 14,209.09 ج.م</t>
+          <t>كود 371 «مفروم فراخ B» ← مفروم فراخ شعبي</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>أكياس تغليف «مقطعات» 5 ك — لا يوجد بند مقابل بالجرد (أكياس 5 ك الموجودة مخصصة لسجق/بانيه/عجينة) — لم تُحمَّل</t>
+          <t>الرتبة B غير موجودة بالجرد؛ سعرها 34 داخل نطاق الرتبة C (30–35) فحُمّلت على «شعبي» — يُراجَع</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>فرق كمية مع ملف «-2»</t>
+          <t>سعر شاذ (دخل كما سُجّل)</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>ثوم</t>
+          <t>سطر 76 كود 190 «صميد»</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>الجرد المعدَّل «جر د شهر 8» = 1249.55 مقابل 1249.3 بملف «-2» — اعتُمد الجرد الفعلى؛ الأثر على قيمة أول المدة +6.27 ج.م</t>
+          <t>نفس ربط الكود فى يوليو: تطابق اسمى تام | ⚠ صميد 50 كجم بسعر 26.40 مقابل 16.25–17.00 لباقى الأسطر</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>فرق كمية مع ملف «-2»</t>
+          <t>شراء بلا مقابل</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>اكياس برجر s.p صغير</t>
+          <t>كود 442 «اكياس تغليف مقطعات 5ك» — 14,209.09 ج.م</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>الجرد المعدَّل «جر د شهر 8» = 259.55 مقابل 260.15 بملف «-2» — اعتُمد الجرد الفعلى؛ الأثر على قيمة أول المدة -139.15 ج.م</t>
+          <t>أكياس تغليف «مقطعات» 5 ك — لا يوجد بند مقابل بالجرد (أكياس 5 ك الموجودة مخصصة لسجق/بانيه/عجينة) — لم تُحمَّل</t>
         </is>
       </c>
     </row>
@@ -31905,46 +32233,46 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>زيت سيارات</t>
+          <t>ثوم</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>الجرد المعدَّل «جر د شهر 8» = 2 مقابل 16 بملف «-2» — اعتُمد الجرد الفعلى؛ الأثر على قيمة أول المدة -18,900.00 ج.م</t>
+          <t>الجرد المعدَّل «جر د شهر 8» = 1249.55 مقابل 1249.3 بملف «-2» — اعتُمد الجرد الفعلى؛ الأثر على قيمة أول المدة +6.27 ج.م</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>صنف بلا سعر</t>
+          <t>فرق كمية مع ملف «-2»</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>كروت كبده علب 350 — كمية جرد 30/9 = 13,373.00</t>
+          <t>اكياس برجر s.p صغير</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>بلا سعر — لا سعر أغسطس ولا مشتريات سبتمبر</t>
+          <t>الجرد المعدَّل «جر د شهر 8» = 259.55 مقابل 260.15 بملف «-2» — اعتُمد الجرد الفعلى؛ الأثر على قيمة أول المدة -139.15 ج.م</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>صنف بلا سعر</t>
+          <t>فرق كمية مع ملف «-2»</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>كروت استربس — كمية جرد 30/9 = 2,000.00</t>
+          <t>زيت سيارات</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>بلا سعر — لا سعر أغسطس ولا مشتريات سبتمبر</t>
+          <t>الجرد المعدَّل «جر د شهر 8» = 2 مقابل 16 بملف «-2» — اعتُمد الجرد الفعلى؛ الأثر على قيمة أول المدة -18,900.00 ج.م</t>
         </is>
       </c>
     </row>
@@ -31956,7 +32284,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>كروت مفروم صافي 350 — كمية جرد 30/9 = 8,818.00</t>
+          <t>كروت كبده علب 350 — كمية جرد 30/9 = 13,373.00</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -31973,7 +32301,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>كروت مفروم صويا 350 — كمية جرد 30/9 = 7,887.00</t>
+          <t>كروت استربس — كمية جرد 30/9 = 2,000.00</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -31990,7 +32318,7 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>كروت برجر أبو هاشم — كمية جرد 30/9 = 2,000.00</t>
+          <t>كروت مفروم صافي 350 — كمية جرد 30/9 = 8,818.00</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -32007,7 +32335,7 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>طبق مسطح 1/2 شفاف — كمية جرد 30/9 = 385.00</t>
+          <t>كروت مفروم صويا 350 — كمية جرد 30/9 = 7,887.00</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -32019,34 +32347,34 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>ملاحظة على جرد 31/8</t>
+          <t>صنف بلا سعر</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>خام عجينة برجر أبو هاشم</t>
+          <t>كروت برجر أبو هاشم — كمية جرد 30/9 = 2,000.00</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>الإجمالى مُدخل يدويًا (0) بينما مجموع المواقع 16.5 — اعتُمد مجموع المواقع</t>
+          <t>بلا سعر — لا سعر أغسطس ولا مشتريات سبتمبر</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>ملاحظة على جرد 31/8</t>
+          <t>صنف بلا سعر</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>خام عجينة كفته الهنا</t>
+          <t>طبق مسطح 1/2 شفاف — كمية جرد 30/9 = 385.00</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>الإجمالى مُدخل يدويًا (0) بينما مجموع المواقع 6.5 — اعتُمد مجموع المواقع</t>
+          <t>بلا سعر — لا سعر أغسطس ولا مشتريات سبتمبر</t>
         </is>
       </c>
     </row>
@@ -32058,27 +32386,61 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>فلتر هواء</t>
+          <t>خام عجينة برجر أبو هاشم</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>الإجمالى مُدخل يدويًا (0) بينما مجموع المواقع 7 — اعتُمد مجموع المواقع</t>
+          <t>الإجمالى مُدخل يدويًا (0) بينما مجموع المواقع 16.5 — اعتُمد مجموع المواقع</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
+          <t>ملاحظة على جرد 31/8</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>خام عجينة كفته الهنا</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>الإجمالى مُدخل يدويًا (0) بينما مجموع المواقع 6.5 — اعتُمد مجموع المواقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>ملاحظة على جرد 31/8</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>فلتر هواء</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>الإجمالى مُدخل يدويًا (0) بينما مجموع المواقع 7 — اعتُمد مجموع المواقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
           <t>منتج تام بلا سعر</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>مفروم ابو هاشم 3 ك — كمية 9.00</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>بلا وصفة ولا سعر سابق — يلزم توفير سعره</t>
         </is>
